--- a/results/batch_export.xlsx
+++ b/results/batch_export.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J327"/>
+  <dimension ref="A1:J331"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -666,7 +666,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bearbeitet: (Datum/Kürzel)</t>
+          <t>Bearbeitet (Datum/Kürzel)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -799,7 +799,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ole Herid-Schimic</t>
+          <t>Ole Herial-Silimi</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -833,7 +833,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ohe</t>
+          <t>ole</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>10.06.2026 / oh</t>
+          <t>10.06.2026 / ah</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1380,7 +1380,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>ABCE 12345 123</t>
+          <t>123</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1389,7 +1389,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.995</v>
+        <v>0.998</v>
       </c>
       <c r="J29" t="inlineStr"/>
     </row>
@@ -1649,32 +1649,33 @@
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>temperature_setpoint</t>
+          <t>hold_end</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Haltetemperatur</t>
+          <t>Erlaubte Haltezeit</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>2026-06-10T14:46:00</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Uhr</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>auto_accepted</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>warning:EXTRACT_LOW_CONF</t>
-        </is>
-      </c>
+        <v>0.995</v>
+      </c>
+      <c r="J36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1688,22 +1689,17 @@
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>hold_end</t>
+          <t>signature_processed</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Erlaubte Haltezeit</t>
+          <t>Bearbeitet</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-06-10T14:46:00</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Uhr</t>
+          <t>10.06.2026 / ohr</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1712,7 +1708,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.995</v>
+        <v>0.979</v>
       </c>
       <c r="J37" t="inlineStr"/>
     </row>
@@ -1728,17 +1724,17 @@
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>signature_processed</t>
+          <t>signature_checked</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bearbeitet</t>
+          <t>Geprüft</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>10.06.2026 / ohr</t>
+          <t>10.06.2026 / hag</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -1758,33 +1754,32 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>signature_checked</t>
-        </is>
-      </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Geprüft</t>
+          <t>B10-PP aus Zyklus 1 vorhanden</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>10.06.2026 / hga</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>auto_accepted</t>
+          <t>needs_review</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.979</v>
-      </c>
-      <c r="J39" t="inlineStr"/>
+        <v>0.8</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>warning:EXTRACT_LOW_CONF</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1798,27 +1793,23 @@
       <c r="C40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>B10-PP aus Zyklus 1 vorhanden</t>
+          <t>B10-PP 3019</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>123</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>auto_accepted</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>warning:EXTRACT_LOW_CONF</t>
-        </is>
-      </c>
+        <v>0.97</v>
+      </c>
+      <c r="J40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1830,14 +1821,24 @@
         <v>12</v>
       </c>
       <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>tare_mass</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>B10-PP 3019</t>
+          <t>m Tara</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>kg</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -1846,7 +1847,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.97</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="J41" t="inlineStr"/>
     </row>
@@ -1862,17 +1863,17 @@
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>tare_mass</t>
+          <t>gross_mass</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>m Tara</t>
+          <t>m Brutto</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>400</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -1902,17 +1903,17 @@
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>gross_mass</t>
+          <t>net_mass</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>m Brutto</t>
+          <t>m Netto</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>300</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -1922,13 +1923,17 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>auto_accepted</t>
+          <t>needs_review</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="J43" t="inlineStr"/>
+        <v>0.4</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>error:CALC_NET_MASS</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1942,37 +1947,33 @@
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>net_mass</t>
+          <t>volume</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>m Netto</t>
+          <t>V Netto</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>543</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>L</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>auto_accepted</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>error:CALC_NET_MASS</t>
-        </is>
-      </c>
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="J44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1986,22 +1987,22 @@
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>volume</t>
+          <t>concentration</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>V Netto</t>
+          <t>c B10-PP (Blocking IPC)</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>543</t>
+          <t>12.6</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>g/L</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2026,22 +2027,22 @@
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>concentration</t>
+          <t>hold_start</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>c B10-PP (Blocking IPC)</t>
+          <t>Start Haltezeit</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>2026-06-10T09:46:00</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>g/L</t>
+          <t>Uhr</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2066,17 +2067,17 @@
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>hold_start</t>
+          <t>hold_end</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Start Haltezeit</t>
+          <t>Erlaubte Haltezeit</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-06-10T09:46:00</t>
+          <t>2026-06-10T15:46:00</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2106,22 +2107,17 @@
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>hold_end</t>
+          <t>signature_processed</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Erlaubte Haltezeit</t>
+          <t>Bearbeitet</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-06-10T15:46:00</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Uhr</t>
+          <t>10.06.2026 / ohr</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2146,17 +2142,17 @@
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>signature_processed</t>
+          <t>signature_checked</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Bearbeitet</t>
+          <t>Geprüft</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>10.06.2026 / ohu</t>
+          <t>10.06.2026 / han</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2176,22 +2172,17 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>signature_checked</t>
-        </is>
-      </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Geprüft</t>
+          <t>Temperierung erforderlich</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>10.06.2026 / han</t>
+          <t>Nein, Kapitel 5.4 findet keine Anwendung</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2200,7 +2191,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.998</v>
       </c>
       <c r="J50" t="inlineStr"/>
     </row>
@@ -2216,12 +2207,12 @@
       <c r="C51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Temperierung erforderlich</t>
+          <t>Intermediat B10-PP 67436</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Nein, Kapitel 5.4 findet keine Anwendung</t>
+          <t>678</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2230,7 +2221,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.998</v>
+        <v>0.999</v>
       </c>
       <c r="J51" t="inlineStr"/>
     </row>
@@ -2246,12 +2237,17 @@
       <c r="C52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>B10-PP 67436</t>
+          <t>Transfer aus dem Kühlraum</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>2026-06-09T11:35:00</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Uhr</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2274,19 +2270,19 @@
         <v>14</v>
       </c>
       <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>signature_processed</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Transfer aus dem Kühlraum</t>
+          <t>Bearbeitet</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-06-09T11:35:00</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Uhr</t>
+          <t>10.06.2026 / ohv</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2295,7 +2291,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.999</v>
+        <v>0.983</v>
       </c>
       <c r="J53" t="inlineStr"/>
     </row>
@@ -2311,17 +2307,17 @@
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>signature_processed</t>
+          <t>signature_checked</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Bearbeitet</t>
+          <t>Geprüft</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>10.06.2026 / ohr</t>
+          <t>10.06.2026 / hah</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2341,33 +2337,32 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C55" t="inlineStr"/>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>signature_checked</t>
-        </is>
-      </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Geprüft</t>
+          <t>Temperierung erforderlich</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>10.06.2026 / hah</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>auto_accepted</t>
+          <t>needs_review</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.983</v>
-      </c>
-      <c r="J55" t="inlineStr"/>
+        <v>0.437</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>warning:EXTRACT_LOW_CONF</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2379,29 +2374,30 @@
         <v>15</v>
       </c>
       <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>signature_processed</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Temperierung erforderlich</t>
+          <t>Bearbeitet</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>10.06.2026 / ob</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>auto_accepted</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.437</v>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>warning:EXTRACT_LOW_CONF</t>
-        </is>
-      </c>
+        <v>0.955</v>
+      </c>
+      <c r="J56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2415,17 +2411,17 @@
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>signature_processed</t>
+          <t>signature_checked</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Bearbeitet</t>
+          <t>Geprüft</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>10.06.2026 / obr</t>
+          <t>10.06.2026 / hau</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2448,30 +2444,29 @@
         <v>15</v>
       </c>
       <c r="C58" t="inlineStr"/>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>signature_checked</t>
-        </is>
-      </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Geprüft</t>
+          <t>Intermediat B10-PP 13975</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>10.06.2026 / han</t>
+          <t>534</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>auto_accepted</t>
+          <t>needs_review</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.955</v>
-      </c>
-      <c r="J58" t="inlineStr"/>
+        <v>0.897</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>warning:EXTRACT_LOW_CONF</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2485,27 +2480,28 @@
       <c r="C59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Intermediat</t>
+          <t>Transfer aus dem Kühlraum</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>B10-PP 13975 534</t>
+          <t>2026-06-10T13:41:00</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Uhr</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>auto_accepted</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.897</v>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>warning:EXTRACT_LOW_CONF</t>
-        </is>
-      </c>
+        <v>0.911</v>
+      </c>
+      <c r="J59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2517,19 +2513,19 @@
         <v>15</v>
       </c>
       <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>signature_processed</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Transfer aus dem Kühlraum</t>
+          <t>Bearbeitet</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-06-10T13:41:00</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>Uhr</t>
+          <t>10.06.2026 / obe</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -2538,7 +2534,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.911</v>
+        <v>0.955</v>
       </c>
       <c r="J60" t="inlineStr"/>
     </row>
@@ -2554,17 +2550,17 @@
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
-          <t>signature_processed</t>
+          <t>signature_checked</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Bearbeitet</t>
+          <t>Geprüft</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>10.06.2026 / obr</t>
+          <t>10.06.2026 / hau</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -2584,33 +2580,32 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C62" t="inlineStr"/>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>signature_checked</t>
-        </is>
-      </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Geprüft</t>
+          <t>Pooling erforderlich</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>10.06.2026 / han</t>
+          <t>Ja, weiter im Kapitel</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>auto_accepted</t>
+          <t>needs_review</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.955</v>
-      </c>
-      <c r="J62" t="inlineStr"/>
+        <v>0.8</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>warning:EXTRACT_LOW_CONF</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2622,29 +2617,30 @@
         <v>16</v>
       </c>
       <c r="C63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>signature_processed</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Pooling erforderlich</t>
+          <t>Bearbeitet (Datum/Kürzel)</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ja, weiter im Kapitel</t>
+          <t>10.06.2026 / oh</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>auto_accepted</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>warning:EXTRACT_LOW_CONF</t>
-        </is>
-      </c>
+        <v>0.996</v>
+      </c>
+      <c r="J63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2658,28 +2654,32 @@
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
-          <t>signature_processed</t>
+          <t>signature_checked</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Bearbeitet</t>
+          <t>Geprüft (Datum/Kürzel)</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>10.06.2026 / oh.</t>
+          <t>10.06.2026 / oh</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>auto_accepted</t>
+          <t>needs_review</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.996</v>
-      </c>
-      <c r="J64" t="inlineStr"/>
+        <v>0.4</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>error:4EYES_DISTINCT</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2691,34 +2691,25 @@
         <v>16</v>
       </c>
       <c r="C65" t="inlineStr"/>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>signature_checked</t>
-        </is>
-      </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Geprüft</t>
+          <t>Oven A - Anlagennummer</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>10.06.2026 / oh.</t>
+          <t>A1234</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>auto_accepted</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>error:4EYES_DISTINCT</t>
-        </is>
-      </c>
+        <v>0.996</v>
+      </c>
+      <c r="J65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2732,23 +2723,27 @@
       <c r="C66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Oven A - Anlagennummer</t>
+          <t>Oven A - Einsatzbereit gemäß RL-SOP-00796</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>A1234</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>auto_accepted</t>
+          <t>needs_review</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.996</v>
-      </c>
-      <c r="J66" t="inlineStr"/>
+        <v>0.8</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>warning:EXTRACT_LOW_CONF</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2762,27 +2757,23 @@
       <c r="C67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Oven A - Einsatzbereit gemäß RL-SOP-00796</t>
+          <t>Batter Pump - Anlagennummer</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>A4265</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>auto_accepted</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>warning:EXTRACT_LOW_CONF</t>
-        </is>
-      </c>
+        <v>0.991</v>
+      </c>
+      <c r="J67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2796,23 +2787,27 @@
       <c r="C68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Batter Pump - Anlagennummer</t>
+          <t>Batter Pump - Einsatzbereit gemäß RL-SOP-00796</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>A4265</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>auto_accepted</t>
+          <t>needs_review</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.991</v>
-      </c>
-      <c r="J68" t="inlineStr"/>
+        <v>0.8</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>warning:EXTRACT_LOW_CONF</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2826,27 +2821,23 @@
       <c r="C69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Batter Pump - Einsatzbereit gemäß RL-SOP-00796</t>
+          <t>Floor Scale - Anlagennummer</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>A321</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>auto_accepted</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>warning:EXTRACT_LOW_CONF</t>
-        </is>
-      </c>
+        <v>0.991</v>
+      </c>
+      <c r="J69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2860,23 +2851,27 @@
       <c r="C70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Floor Scale - Anlagennummer</t>
+          <t>Floor Scale - Einsatzbereit gemäß RL-SOP-00796</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>A321</t>
+          <t>Kein Einsatz</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>auto_accepted</t>
+          <t>needs_review</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.991</v>
-      </c>
-      <c r="J70" t="inlineStr"/>
+        <v>0.8</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>warning:EXTRACT_LOW_CONF</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2890,27 +2885,23 @@
       <c r="C71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Floor Scale - Einsatzbereit gemäß RL-SOP-00796</t>
+          <t>Bench Scale - Anlagennummer</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kein Einsatz</t>
+          <t>A45978</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>auto_accepted</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>warning:EXTRACT_LOW_CONF</t>
-        </is>
-      </c>
+        <v>0.991</v>
+      </c>
+      <c r="J71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2924,23 +2915,27 @@
       <c r="C72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Bench Scale - Anlagennummer</t>
+          <t>Bench Scale - Einsatzbereit gemäß RL-SOP-00796</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>A45978</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>auto_accepted</t>
+          <t>needs_review</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.991</v>
-      </c>
-      <c r="J72" t="inlineStr"/>
+        <v>0.8</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>warning:EXTRACT_LOW_CONF</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2954,27 +2949,23 @@
       <c r="C73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Bench Scale - Einsatzbereit gemäß RL-SOP-00796</t>
+          <t>Bowl Rocker - Anlagennummer</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>A32141</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>auto_accepted</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>warning:EXTRACT_LOW_CONF</t>
-        </is>
-      </c>
+        <v>0.991</v>
+      </c>
+      <c r="J73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2988,23 +2979,27 @@
       <c r="C74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Bowl Rocker - Anlagennummer</t>
+          <t>Bowl Rocker - Einsatzbereit gemäß RL-SOP-00796</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>A32141</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>auto_accepted</t>
+          <t>needs_review</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.991</v>
-      </c>
-      <c r="J74" t="inlineStr"/>
+        <v>0.8</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>warning:EXTRACT_LOW_CONF</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3013,32 +3008,38 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>hold_start</t>
+        </is>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Bowl Rocker - Einsatzbereit gemäß RL-SOP-00796</t>
+          <t>Start Überführung</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>09:26:00</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Uhr</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>auto_accepted</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>warning:EXTRACT_LOW_CONF</t>
-        </is>
-      </c>
+        <v>0.997</v>
+      </c>
+      <c r="J75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3052,17 +3053,17 @@
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
-          <t>hold_start</t>
+          <t>hold_end</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Start Überführung</t>
+          <t>Ende Überführung</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>09:26:00</t>
+          <t>10:12:00</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -3076,7 +3077,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.997</v>
+        <v>0.993</v>
       </c>
       <c r="J76" t="inlineStr"/>
     </row>
@@ -3090,35 +3091,34 @@
         <v>17</v>
       </c>
       <c r="C77" t="inlineStr"/>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>hold_end</t>
-        </is>
-      </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Ende Überführung</t>
+          <t>Wippgeschwindigkeit</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>10:12:00</t>
+          <t>32</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Uhr</t>
+          <t>Hübe/min</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>auto_accepted</t>
+          <t>needs_review</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.993</v>
-      </c>
-      <c r="J77" t="inlineStr"/>
+        <v>0.4</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>error:RANGE_SOLL</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3130,34 +3130,35 @@
         <v>17</v>
       </c>
       <c r="C78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>hold_start</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Wippgeschwindigkeit</t>
+          <t>Start Homogenisieren</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>10:12:00</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hübe/min</t>
+          <t>Uhr</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>auto_accepted</t>
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>error:RANGE_SOLL</t>
-        </is>
-      </c>
+        <v>0.993</v>
+      </c>
+      <c r="J78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3171,17 +3172,17 @@
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
-          <t>hold_start</t>
+          <t>hold_end</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Start Homogenisieren</t>
+          <t>Ende Homogenisieren</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>10:12:00</t>
+          <t>10:24:00</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -3195,7 +3196,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.993</v>
+        <v>0.999</v>
       </c>
       <c r="J79" t="inlineStr"/>
     </row>
@@ -3216,17 +3217,17 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Ende Homogenisieren</t>
+          <t>Dauer Homogenisieren nach Ende Überführung</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>10:24:00</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Uhr</t>
+          <t>min</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -3235,7 +3236,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.999</v>
+        <v>0.996</v>
       </c>
       <c r="J80" t="inlineStr"/>
     </row>
@@ -3249,24 +3250,14 @@
         <v>17</v>
       </c>
       <c r="C81" t="inlineStr"/>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>hold_end</t>
-        </is>
-      </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Dauer Homogenisieren nach Ende Überführung</t>
+          <t>Neues Intermediat</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>min</t>
+          <t>B20-ST 9784 697</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -3275,7 +3266,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.996</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="J81" t="inlineStr"/>
     </row>
@@ -3289,25 +3280,34 @@
         <v>17</v>
       </c>
       <c r="C82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>signature_processed</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Neues Intermediat</t>
+          <t>Bearbeitet</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>B20-ST 9784 697</t>
+          <t>10.06.2028 / ole</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>auto_accepted</t>
+          <t>needs_review</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.9379999999999999</v>
-      </c>
-      <c r="J82" t="inlineStr"/>
+        <v>0.7</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>warning:DATE_FAR_FUTURE</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3321,17 +3321,17 @@
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
-          <t>signature_processed</t>
+          <t>signature_checked</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Bearbeitet</t>
+          <t>Geprüft</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>10.06.2028 / dkr</t>
+          <t>10.06.2028 / hah</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -3340,11 +3340,11 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>warning:EXTRACT_LOW_CONF</t>
+          <t>warning:DATE_FAR_FUTURE</t>
         </is>
       </c>
     </row>
@@ -3355,37 +3355,28 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C84" t="inlineStr"/>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>signature_checked</t>
-        </is>
-      </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Geprüft</t>
+          <t>Oven A Anlagen-nummer</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>10.06.2028 / hah</t>
+          <t>A1473</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>auto_accepted</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>warning:EXTRACT_LOW_CONF</t>
-        </is>
-      </c>
+        <v>0.99</v>
+      </c>
+      <c r="J84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3399,23 +3390,27 @@
       <c r="C85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Oven A - Anlagen-nummer</t>
+          <t>Oven A Einsatzbereit gemäß RL-SOP-00796</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>A1473</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>auto_accepted</t>
+          <t>needs_review</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="J85" t="inlineStr"/>
+        <v>0.8</v>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>warning:EXTRACT_LOW_CONF</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3429,27 +3424,23 @@
       <c r="C86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Oven A - Einsatzbereit gemäß RL-SOP-00796</t>
+          <t>Floor Scale Anlagen-nummer</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>A3215</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>auto_accepted</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>warning:EXTRACT_LOW_CONF</t>
-        </is>
-      </c>
+        <v>0.99</v>
+      </c>
+      <c r="J86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3463,23 +3454,27 @@
       <c r="C87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Floor Scale - Anlagen-nummer</t>
+          <t>Floor Scale Einsatzbereit gemäß RL-SOP-00796</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>A3215</t>
+          <t>Kein Einsatz</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>auto_accepted</t>
+          <t>needs_review</t>
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="J87" t="inlineStr"/>
+        <v>0.8</v>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>warning:EXTRACT_LOW_CONF</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3493,27 +3488,23 @@
       <c r="C88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Floor Scale - Einsatzbereit gemäß RL-SOP-00796</t>
+          <t>Bench Scale Anlagen-nummer</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kein Einsatz</t>
+          <t>A5114</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>auto_accepted</t>
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>warning:EXTRACT_LOW_CONF</t>
-        </is>
-      </c>
+        <v>0.99</v>
+      </c>
+      <c r="J88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3527,23 +3518,27 @@
       <c r="C89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Bench Scale - Anlagen-nummer</t>
+          <t>Bench Scale Einsatzbereit gemäß RL-SOP-00796</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>A5114</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>auto_accepted</t>
+          <t>needs_review</t>
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="J89" t="inlineStr"/>
+        <v>0.8</v>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>warning:EXTRACT_LOW_CONF</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3557,27 +3552,23 @@
       <c r="C90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Bench Scale - Einsatzbereit gemäß RL-SOP-00796</t>
+          <t>Bowl Rocker Anlagen-nummer</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>A4662</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>auto_accepted</t>
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>warning:EXTRACT_LOW_CONF</t>
-        </is>
-      </c>
+        <v>0.99</v>
+      </c>
+      <c r="J90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3591,23 +3582,27 @@
       <c r="C91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Bowl Rocker - Anlagen-nummer</t>
+          <t>Bowl Rocker Einsatzbereit gemäß RL-SOP-00796</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>A4662</t>
+          <t>Kein Einsatz</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>auto_accepted</t>
+          <t>needs_review</t>
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="J91" t="inlineStr"/>
+        <v>0.8</v>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>warning:EXTRACT_LOW_CONF</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3621,27 +3616,23 @@
       <c r="C92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Bowl Rocker - Einsatzbereit gemäß RL-SOP-00796</t>
+          <t>Thermometer / Moisture Meter Anlagen-nummer</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kein Einsatz</t>
+          <t>A8498</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>auto_accepted</t>
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>warning:EXTRACT_LOW_CONF</t>
-        </is>
-      </c>
+        <v>0.99</v>
+      </c>
+      <c r="J92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3655,23 +3646,27 @@
       <c r="C93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Thermometer / Moisture Meter - Anlagen-nummer</t>
+          <t>Thermometer / Moisture Meter Einsatzbereit gemäß RL-SOP-00796</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>A8498</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>auto_accepted</t>
+          <t>needs_review</t>
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="J93" t="inlineStr"/>
+        <v>0.8</v>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>warning:EXTRACT_LOW_CONF</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3683,29 +3678,30 @@
         <v>18</v>
       </c>
       <c r="C94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>signature_processed</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Thermometer / Moisture Meter - Einsatzbereit gemäß RL-SOP-00796</t>
+          <t>Bearbeitet (Datum/Kürzel)</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>10.06.2026 / oho</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>auto_accepted</t>
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>warning:EXTRACT_LOW_CONF</t>
-        </is>
-      </c>
+        <v>0.99</v>
+      </c>
+      <c r="J94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3719,17 +3715,17 @@
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
-          <t>signature_processed</t>
+          <t>signature_checked</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Bearbeitet (Datum/Kürzel)</t>
+          <t>Geprüft (Datum/Kürzel)</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>10.06.2026 / ohp</t>
+          <t>10.06.2026 / hän</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -3749,22 +3745,17 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C96" t="inlineStr"/>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>signature_checked</t>
-        </is>
-      </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Geprüft (Datum/Kürzel)</t>
+          <t>Nur ein B10-PP vorhanden?</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>10.06.2026 / häh</t>
+          <t>Ja, Übertrag der Daten aus Kapitel 5.3.1</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -3773,7 +3764,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.99</v>
+        <v>0.992</v>
       </c>
       <c r="J96" t="inlineStr"/>
     </row>
@@ -3789,12 +3780,12 @@
       <c r="C97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Nur ein B10-PP vorhanden?</t>
+          <t>B20-ST 95186</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ja, Übertrag der Daten aus Kapitel 5.3.1</t>
+          <t>327</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -3817,14 +3808,24 @@
         <v>19</v>
       </c>
       <c r="C98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>tare_mass</t>
+        </is>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>B20-ST 95186</t>
+          <t>m Tara</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>327</t>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>kg</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -3849,17 +3850,17 @@
       <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr">
         <is>
-          <t>tare_mass</t>
+          <t>gross_mass</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>m Tara</t>
+          <t>m Brutto vPz</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>427</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -3889,17 +3890,17 @@
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr">
         <is>
-          <t>gross_mass</t>
+          <t>net_mass</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>m Brutto vPz</t>
+          <t>m Netto vPz</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>427</t>
+          <t>300</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -3929,22 +3930,22 @@
       <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr">
         <is>
-          <t>net_mass</t>
+          <t>volume</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>m Netto vPz</t>
+          <t>V Netto vPz</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>543</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>L</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -3967,35 +3968,29 @@
         <v>19</v>
       </c>
       <c r="C102" t="inlineStr"/>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>volume</t>
-        </is>
-      </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>V Netto vPz</t>
+          <t>Proben (GPDSP) gemäß BK-MAN-01825 erforderlich (siehe Kapitel 6.7.4)</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>543</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>L</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>auto_accepted</t>
+          <t>needs_review</t>
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.992</v>
-      </c>
-      <c r="J102" t="inlineStr"/>
+        <v>0.8</v>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>warning:EXTRACT_LOW_CONF</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -4009,7 +4004,7 @@
       <c r="C103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Proben (GPDSP) gemäß BK-MAN-01825 erforderlich (siehe Kapitel 6.7.4)</t>
+          <t>Proben (QC) gemäß BK-MAN-16865 erforderlich</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4043,12 +4038,12 @@
       <c r="C104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Proben (QC) gemäß BK-MAN-16865 erforderlich</t>
+          <t>Proben gemäß Sonderprobenzugplan erforderlich</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>Nein</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -4077,12 +4072,12 @@
       <c r="C105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Proben gemäß Sonderprobenzugsplan erforderlich</t>
+          <t>Taste Sample aller Proben nach Überprüfung in LIMS durchgeführt</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Nein</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -4109,29 +4104,35 @@
         <v>19</v>
       </c>
       <c r="C106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>gross_mass</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Taste Sample aller Proben nach Überprüfung in LIMS durchgeführt</t>
+          <t>m Brutto nPZ</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>527</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>kg</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>auto_accepted</t>
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>warning:EXTRACT_LOW_CONF</t>
-        </is>
-      </c>
+        <v>0.992</v>
+      </c>
+      <c r="J106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -4145,17 +4146,17 @@
       <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr">
         <is>
-          <t>gross_mass</t>
+          <t>net_mass</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>m Brutto nPZ</t>
+          <t>m Netto nPZ</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>527</t>
+          <t>395</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -4185,22 +4186,22 @@
       <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr">
         <is>
-          <t>net_mass</t>
+          <t>volume</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>m Netto nPZ</t>
+          <t>V Netto nPZ</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>395</t>
+          <t>715</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>L</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -4225,22 +4226,17 @@
       <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr">
         <is>
-          <t>volume</t>
+          <t>signature_processed</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>V Netto nPZ</t>
+          <t>Bearbeitet</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>715</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>L</t>
+          <t>10.06.2026 / ohe</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -4249,7 +4245,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.992</v>
+        <v>0.975</v>
       </c>
       <c r="J109" t="inlineStr"/>
     </row>
@@ -4265,17 +4261,17 @@
       <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr">
         <is>
-          <t>signature_processed</t>
+          <t>signature_checked</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Bearbeitet</t>
+          <t>Geprüft</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>10.06.2026 / ohe</t>
+          <t>10.06.2026 / han</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -4295,33 +4291,32 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C111" t="inlineStr"/>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>signature_checked</t>
-        </is>
-      </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Geprüft</t>
+          <t>LIMS basierten Probenzug durchgeführt</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>10.06.2026 / han</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>auto_accepted</t>
+          <t>needs_review</t>
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.975</v>
-      </c>
-      <c r="J111" t="inlineStr"/>
+        <v>0.8</v>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>warning:EXTRACT_LOW_CONF</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4335,27 +4330,28 @@
       <c r="C112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>LIMS basierten Probenzug durchgeführt</t>
+          <t>Probenzug</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>15:26:00</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Uhr</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>auto_accepted</t>
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>warning:EXTRACT_LOW_CONF</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="J112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4369,28 +4365,27 @@
       <c r="C113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Probenzug</t>
+          <t>Probenzugsetikett(en) auf Probe(n) mit eingeklebtem(n) Etikett(en) identisch</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>15:26:00</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>Uhr</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>auto_accepted</t>
+          <t>needs_review</t>
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1</v>
-      </c>
-      <c r="J113" t="inlineStr"/>
+        <v>0.8</v>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>warning:EXTRACT_LOW_CONF</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4404,7 +4399,7 @@
       <c r="C114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Probenzugsetikett(en) auf Probe(n) mit eingeklebtem(n) Etikett(en) identisch</t>
+          <t>A representative taste and appearance sample is taken from the batter or baked cake according to the defined sampling plan. The label is verified, the sample is stored appropriately, and the observation is documented in a GMP-like manner for traceability.</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4438,7 +4433,7 @@
       <c r="C115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>A representative taste and appearance sample is taken from the batter or baked cake according to the defined sampling plan. The label is verified, the sample is stored appropriately, and the observation is documented in a GMP-like manner for traceability.</t>
+          <t>Plan für betroffene Prozessstufe vollständig (grün)</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4470,29 +4465,30 @@
         <v>20</v>
       </c>
       <c r="C116" t="inlineStr"/>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>signature_processed</t>
+        </is>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Plan für betroffene Prozessstufe vollständig (grün)</t>
+          <t>Bearbeitet</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>10.06.2026 / dhe</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>auto_accepted</t>
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>warning:EXTRACT_LOW_CONF</t>
-        </is>
-      </c>
+        <v>0.998</v>
+      </c>
+      <c r="J116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4506,17 +4502,17 @@
       <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr">
         <is>
-          <t>signature_processed</t>
+          <t>signature_checked</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Bearbeitet</t>
+          <t>Geprüft</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>10.06.2026 / che</t>
+          <t>10.06.2026 / hau</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -4536,22 +4532,22 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C118" t="inlineStr"/>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>signature_checked</t>
-        </is>
-      </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Geprüft</t>
+          <t>LF B20-ST</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>10.06.2026 / hay</t>
+          <t>14.34</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>mS/cm</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -4560,7 +4556,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.998</v>
+        <v>0.996</v>
       </c>
       <c r="J118" t="inlineStr"/>
     </row>
@@ -4574,19 +4570,19 @@
         <v>21</v>
       </c>
       <c r="C119" t="inlineStr"/>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>signature_processed</t>
+        </is>
+      </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>LF B20-ST</t>
+          <t>Bearbeitet</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>14.34</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>mS/cm</t>
+          <t>10.06.2026 / Ohe</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -4595,7 +4591,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>0.996</v>
+        <v>0.997</v>
       </c>
       <c r="J119" t="inlineStr"/>
     </row>
@@ -4611,17 +4607,17 @@
       <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr">
         <is>
-          <t>signature_processed</t>
+          <t>signature_checked</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Bearbeitet</t>
+          <t>Geprüft</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>10.06.2026 / ohe</t>
+          <t>10.06.2026 / hsu</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -4641,33 +4637,32 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C121" t="inlineStr"/>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>signature_checked</t>
-        </is>
-      </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Geprüft</t>
+          <t>Prozessverzögerung</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>10.06.2026 / hsu</t>
+          <t>Nein, Kapitel findet keine Anwendung</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>auto_accepted</t>
+          <t>needs_review</t>
         </is>
       </c>
       <c r="I121" t="n">
-        <v>0.997</v>
-      </c>
-      <c r="J121" t="inlineStr"/>
+        <v>0.8</v>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>warning:EXTRACT_LOW_CONF</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4679,29 +4674,30 @@
         <v>23</v>
       </c>
       <c r="C122" t="inlineStr"/>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>signature_processed</t>
+        </is>
+      </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Prozessverzögerung</t>
+          <t>Bearbeitet</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Nein, Kapitel findet keine Anwendung</t>
+          <t>10.06.2026 / ohe</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>auto_accepted</t>
         </is>
       </c>
       <c r="I122" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>warning:EXTRACT_LOW_CONF</t>
-        </is>
-      </c>
+        <v>0.989</v>
+      </c>
+      <c r="J122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4715,12 +4711,12 @@
       <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr">
         <is>
-          <t>signature_processed</t>
+          <t>signature_checked</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Bearbeitet</t>
+          <t>Geprüft</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4730,13 +4726,17 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>auto_accepted</t>
+          <t>needs_review</t>
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0.989</v>
-      </c>
-      <c r="J123" t="inlineStr"/>
+        <v>0.4</v>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>error:4EYES_DISTINCT</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4750,32 +4750,33 @@
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr">
         <is>
-          <t>signature_checked</t>
+          <t>hold_start</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Geprüft</t>
+          <t>Start Prozessverzögerung</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>10.06.2026 / ohe</t>
+          <t>11:27:00</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Uhr</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>auto_accepted</t>
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>error:4EYES_DISTINCT</t>
-        </is>
-      </c>
+        <v>0.987</v>
+      </c>
+      <c r="J124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4789,33 +4790,32 @@
       <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr">
         <is>
-          <t>hold_start</t>
+          <t>temperature_setpoint</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Start Prozessverzögerung</t>
+          <t>Haltetemperatur</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>11:27:00</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>Uhr</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>auto_accepted</t>
+          <t>needs_review</t>
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.987</v>
-      </c>
-      <c r="J125" t="inlineStr"/>
+        <v>0.8</v>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>warning:EXTRACT_LOW_CONF</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4829,37 +4829,28 @@
       <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr">
         <is>
-          <t>temperature_setpoint</t>
+          <t>signature_processed</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Haltetemperatur</t>
+          <t>Bearbeitet</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>°C</t>
+          <t>10.06.2026 / ohe</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>auto_accepted</t>
         </is>
       </c>
       <c r="I126" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J126" t="inlineStr">
-        <is>
-          <t>warning:EXTRACT_LOW_CONF</t>
-        </is>
-      </c>
+        <v>0.989</v>
+      </c>
+      <c r="J126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4873,17 +4864,17 @@
       <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr">
         <is>
-          <t>signature_processed</t>
+          <t>signature_checked</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Bearbeitet</t>
+          <t>Geprüft</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>10.06.2026 / ohe</t>
+          <t>10.06.2026 / haa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -4908,17 +4899,22 @@
       <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr">
         <is>
-          <t>signature_checked</t>
+          <t>hold_end</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Geprüft</t>
+          <t>Ende Prozessverzögerung</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>10.06.2026 / han</t>
+          <t>12:27:00</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Uhr</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -4927,7 +4923,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0.989</v>
+        <v>0.99</v>
       </c>
       <c r="J128" t="inlineStr"/>
     </row>
@@ -4941,24 +4937,19 @@
         <v>23</v>
       </c>
       <c r="C129" t="inlineStr"/>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>hold_end</t>
-        </is>
-      </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Ende Prozessverzögerung</t>
+          <t>Tatsächliche Prozessverzögerung</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>12:27:00</t>
+          <t>02:00:00</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Uhr</t>
+          <t>h</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -4983,28 +4974,27 @@
       <c r="C130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Tatsächliche Prozessverzögerung</t>
+          <t>Prozessverzögerung &gt; 4 h</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>02:00:00</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>h</t>
+          <t>Nein</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>auto_accepted</t>
+          <t>needs_review</t>
         </is>
       </c>
       <c r="I130" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="J130" t="inlineStr"/>
+        <v>0.8</v>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>warning:EXTRACT_LOW_CONF</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -5016,29 +5006,30 @@
         <v>23</v>
       </c>
       <c r="C131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>signature_processed</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Prozessverzögerung &gt; 4 h</t>
+          <t>Bearbeitet</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Nein</t>
+          <t>10.06.2026 / ohe</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>auto_accepted</t>
         </is>
       </c>
       <c r="I131" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>warning:EXTRACT_LOW_CONF</t>
-        </is>
-      </c>
+        <v>0.989</v>
+      </c>
+      <c r="J131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -5052,17 +5043,17 @@
       <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr">
         <is>
-          <t>signature_processed</t>
+          <t>signature_checked</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Bearbeitet</t>
+          <t>Geprüft</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>10.06.2026 / ohe</t>
+          <t>10.06.2026 / haa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -5082,22 +5073,17 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C133" t="inlineStr"/>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>signature_checked</t>
-        </is>
-      </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Geprüft</t>
+          <t>Charge</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>10.06.2026 / han</t>
+          <t>1234567</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -5106,7 +5092,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>0.989</v>
+        <v>0.985</v>
       </c>
       <c r="J133" t="inlineStr"/>
     </row>
@@ -5122,12 +5108,12 @@
       <c r="C134" t="inlineStr"/>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Charge</t>
+          <t>Ofenfreigabe erteilt zum</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>1234567</t>
+          <t>2019-03-14</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -5152,12 +5138,17 @@
       <c r="C135" t="inlineStr"/>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Ofenfreigabe erteilt zum</t>
+          <t>Baker Five</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2019-03-14</t>
+          <t>3.78</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>cm</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -5182,12 +5173,12 @@
       <c r="C136" t="inlineStr"/>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Baker Five</t>
+          <t>Baker Seven</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -5215,19 +5206,24 @@
         <v>24</v>
       </c>
       <c r="C137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>volume</t>
+        </is>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Baker Seven</t>
+          <t>Baker Eigth</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>cm</t>
+          <t>L</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -5252,33 +5248,32 @@
       <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr">
         <is>
-          <t>volume</t>
+          <t>signature_processed</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Baker Eigth</t>
+          <t>Bearbeitet</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>1.62</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>L</t>
+          <t>10.06.2025 / ohe</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>auto_accepted</t>
+          <t>needs_review</t>
         </is>
       </c>
       <c r="I138" t="n">
-        <v>0.985</v>
-      </c>
-      <c r="J138" t="inlineStr"/>
+        <v>0.7</v>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>warning:DATE_BEFORE_PRINT</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -5290,29 +5285,30 @@
         <v>24</v>
       </c>
       <c r="C139" t="inlineStr"/>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>signature_checked</t>
+        </is>
+      </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Ofen in Oven List mit aufgelisteten Parametern erfasst</t>
+          <t>Geprüft</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>10.06.2026 / haa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>auto_accepted</t>
         </is>
       </c>
       <c r="I139" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J139" t="inlineStr">
-        <is>
-          <t>warning:EXTRACT_LOW_CONF</t>
-        </is>
-      </c>
+        <v>0.971</v>
+      </c>
+      <c r="J139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -5326,17 +5322,17 @@
       <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr">
         <is>
-          <t>signature_processed</t>
+          <t>hold_end</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Bearbeitet</t>
+          <t>Zuletzt verwendet für Production Code</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>10.06.2025 / ohe</t>
+          <t>327</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -5345,7 +5341,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>0.971</v>
+        <v>0.986</v>
       </c>
       <c r="J140" t="inlineStr"/>
     </row>
@@ -5359,30 +5355,29 @@
         <v>24</v>
       </c>
       <c r="C141" t="inlineStr"/>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>signature_checked</t>
-        </is>
-      </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Geprüft</t>
+          <t>Anzahl der bisherigen Zyklen</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>10.06.2026 / hah</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>auto_accepted</t>
+          <t>needs_review</t>
         </is>
       </c>
       <c r="I141" t="n">
-        <v>0.971</v>
-      </c>
-      <c r="J141" t="inlineStr"/>
+        <v>0.8</v>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>warning:EXTRACT_LOW_CONF</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -5394,30 +5389,29 @@
         <v>24</v>
       </c>
       <c r="C142" t="inlineStr"/>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>hold_end</t>
-        </is>
-      </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Zuletzt verwendet für Production Code</t>
+          <t>Ofen in SAP ausgebucht</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>57497 327</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>auto_accepted</t>
+          <t>needs_review</t>
         </is>
       </c>
       <c r="I142" t="n">
-        <v>0.986</v>
-      </c>
-      <c r="J142" t="inlineStr"/>
+        <v>0.8</v>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>warning:EXTRACT_LOW_CONF</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -5431,12 +5425,12 @@
       <c r="C143" t="inlineStr"/>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Anzahl der bisherigen Zyklen</t>
+          <t>Testlauf der ChromatographieOfen „BAK B20 AXXXX SuitTest“ vor Verwendung durchgeführt und bestanden (nur bei Anzahl der bisherigen Zyklen ≥ 2)</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -5463,29 +5457,30 @@
         <v>24</v>
       </c>
       <c r="C144" t="inlineStr"/>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>signature_processed</t>
+        </is>
+      </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Ofen in SAP ausgebucht</t>
+          <t>Bearbeitet</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>10.06.2026 / ohe</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>auto_accepted</t>
         </is>
       </c>
       <c r="I144" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J144" t="inlineStr">
-        <is>
-          <t>warning:EXTRACT_LOW_CONF</t>
-        </is>
-      </c>
+        <v>0.971</v>
+      </c>
+      <c r="J144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5497,29 +5492,30 @@
         <v>24</v>
       </c>
       <c r="C145" t="inlineStr"/>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>signature_checked</t>
+        </is>
+      </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Testlauf der ChromatographieOfen „BAK B20 AXXXX SuitTest“ vor Verwendung durchgeführt und bestanden (nur bei Anzahl der bisherigen Zyklen ≥ 2)</t>
+          <t>Geprüft</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>10.06.2026 / haa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>auto_accepted</t>
         </is>
       </c>
       <c r="I145" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J145" t="inlineStr">
-        <is>
-          <t>warning:EXTRACT_LOW_CONF</t>
-        </is>
-      </c>
+        <v>0.971</v>
+      </c>
+      <c r="J145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5528,22 +5524,27 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr">
         <is>
-          <t>signature_processed</t>
+          <t>net_mass</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Bearbeitet</t>
+          <t>m B10-PP Netto nPZ Z1</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>10.06.2026 / ohe</t>
+          <t>321</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>kg</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -5552,7 +5553,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>0.971</v>
+        <v>0.989</v>
       </c>
       <c r="J146" t="inlineStr"/>
     </row>
@@ -5563,22 +5564,27 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr">
         <is>
-          <t>signature_checked</t>
+          <t>concentration</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Geprüft</t>
+          <t>c B10-PP Z1</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>10.06.2026 / hah</t>
+          <t>4.35</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>g/L</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -5587,7 +5593,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>0.971</v>
+        <v>0.989</v>
       </c>
       <c r="J147" t="inlineStr"/>
     </row>
@@ -5601,35 +5607,34 @@
         <v>25</v>
       </c>
       <c r="C148" t="inlineStr"/>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>net_mass</t>
-        </is>
-      </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>m B10-PP Netto nPZ z1</t>
+          <t>m B10-PP Z1</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>1065</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>g</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>auto_accepted</t>
+          <t>needs_review</t>
         </is>
       </c>
       <c r="I148" t="n">
-        <v>0.989</v>
-      </c>
-      <c r="J148" t="inlineStr"/>
+        <v>0.7</v>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>warning:CALC_ROUNDING</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5641,35 +5646,29 @@
         <v>25</v>
       </c>
       <c r="C149" t="inlineStr"/>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>concentration</t>
-        </is>
-      </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>c B10-PP z1</t>
+          <t>B10 Zyklus 2 durchgeführt</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>4.35</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>g/L</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>auto_accepted</t>
+          <t>needs_review</t>
         </is>
       </c>
       <c r="I149" t="n">
-        <v>0.989</v>
-      </c>
-      <c r="J149" t="inlineStr"/>
+        <v>0.8</v>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>warning:EXTRACT_LOW_CONF</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -5681,19 +5680,24 @@
         <v>25</v>
       </c>
       <c r="C150" t="inlineStr"/>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>net_mass</t>
+        </is>
+      </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>m B10-PP z1</t>
+          <t>m B10-PP Netto nPZ Z2</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>1065</t>
+          <t>220</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -5716,29 +5720,35 @@
         <v>25</v>
       </c>
       <c r="C151" t="inlineStr"/>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>concentration</t>
+        </is>
+      </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>B10 Zyklus 2 durchgeführt</t>
+          <t>c B10-PP Z2</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>3.94</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>g/L</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>auto_accepted</t>
         </is>
       </c>
       <c r="I151" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J151" t="inlineStr">
-        <is>
-          <t>warning:EXTRACT_LOW_CONF</t>
-        </is>
-      </c>
+        <v>0.989</v>
+      </c>
+      <c r="J151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -5750,24 +5760,19 @@
         <v>25</v>
       </c>
       <c r="C152" t="inlineStr"/>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>net_mass</t>
-        </is>
-      </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>m B10-PP Netto nPZ z2</t>
+          <t>m B10-PP Z2</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>479</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>g</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -5790,24 +5795,19 @@
         <v>25</v>
       </c>
       <c r="C153" t="inlineStr"/>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>concentration</t>
-        </is>
-      </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>c B10-PP z2</t>
+          <t>m B10-PP Z1</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>1065</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>g/L</t>
+          <t>g</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -5832,7 +5832,7 @@
       <c r="C154" t="inlineStr"/>
       <c r="E154" t="inlineStr">
         <is>
-          <t>m B10-PP z2</t>
+          <t>m B10-PP Z2</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -5867,12 +5867,12 @@
       <c r="C155" t="inlineStr"/>
       <c r="E155" t="inlineStr">
         <is>
-          <t>m B10-PP z1</t>
+          <t>m B20-ST</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>1065</t>
+          <t>1544</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -5900,19 +5900,19 @@
         <v>25</v>
       </c>
       <c r="C156" t="inlineStr"/>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>signature_processed</t>
+        </is>
+      </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>m B10-PP z2</t>
+          <t>Bearbeitet</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>479</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>g</t>
+          <t>10.06.2026 / ole</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>0.989</v>
+        <v>0.965</v>
       </c>
       <c r="J156" t="inlineStr"/>
     </row>
@@ -5935,19 +5935,19 @@
         <v>25</v>
       </c>
       <c r="C157" t="inlineStr"/>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>signature_checked</t>
+        </is>
+      </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>m B20-ST</t>
+          <t>Geprüft</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>1544</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>g</t>
+          <t>10.06.2026 / hm</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -5956,7 +5956,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>0.989</v>
+        <v>0.965</v>
       </c>
       <c r="J157" t="inlineStr"/>
     </row>
@@ -5967,22 +5967,22 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C158" t="inlineStr"/>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>signature_processed</t>
-        </is>
-      </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Bearbeitet</t>
+          <t>m B20-ST</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>10.06.2026 / dhe</t>
+          <t>421</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>g</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -5991,7 +5991,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>0.965</v>
+        <v>0.989</v>
       </c>
       <c r="J158" t="inlineStr"/>
     </row>
@@ -6002,33 +6002,42 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C159" t="inlineStr"/>
       <c r="D159" t="inlineStr">
         <is>
-          <t>signature_checked</t>
+          <t>volume</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Geprüft</t>
+          <t>V Ofen BAK B20</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>10.06.2026 / hgm</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>auto_accepted</t>
+          <t>needs_review</t>
         </is>
       </c>
       <c r="I159" t="n">
-        <v>0.965</v>
-      </c>
-      <c r="J159" t="inlineStr"/>
+        <v>0.8</v>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>warning:EXTRACT_LOW_CONF</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -6042,17 +6051,17 @@
       <c r="C160" t="inlineStr"/>
       <c r="E160" t="inlineStr">
         <is>
-          <t>m B20-ST</t>
+          <t>Beladung</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>421</t>
+          <t>211</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>g Cake/L Milk</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -6075,24 +6084,14 @@
         <v>26</v>
       </c>
       <c r="C161" t="inlineStr"/>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>volume</t>
-        </is>
-      </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>V Ofen BAK B20</t>
+          <t>Beladung 7 – 19 g Cake/L Milk eingehalten</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>L</t>
+          <t>Nein, Anpassung der Beladung notwendig, Rücksprache mit Leiter</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -6121,28 +6120,27 @@
       <c r="C162" t="inlineStr"/>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Beladung</t>
+          <t>Oven Life Time von 5 Zyklen wird nicht überschritten</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>g Cake/L Milk</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>auto_accepted</t>
+          <t>needs_review</t>
         </is>
       </c>
       <c r="I162" t="n">
-        <v>0.989</v>
-      </c>
-      <c r="J162" t="inlineStr"/>
+        <v>0.8</v>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>warning:EXTRACT_LOW_CONF</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -6154,29 +6152,30 @@
         <v>26</v>
       </c>
       <c r="C163" t="inlineStr"/>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>signature_processed</t>
+        </is>
+      </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Beladung eingehalten</t>
+          <t>Bearbeitet</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Nein, Anpassung der Beladung notwendig, Rücksprache mit Leiter</t>
+          <t>10.06.2026 / ohp</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>auto_accepted</t>
         </is>
       </c>
       <c r="I163" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J163" t="inlineStr">
-        <is>
-          <t>warning:EXTRACT_LOW_CONF</t>
-        </is>
-      </c>
+        <v>0.981</v>
+      </c>
+      <c r="J163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -6188,29 +6187,30 @@
         <v>26</v>
       </c>
       <c r="C164" t="inlineStr"/>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>signature_checked</t>
+        </is>
+      </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Oven Life Time von 5 Zyklen wird nicht überschritten</t>
+          <t>Geprüft</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>10.06.2026 / hgh</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>auto_accepted</t>
         </is>
       </c>
       <c r="I164" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J164" t="inlineStr">
-        <is>
-          <t>warning:EXTRACT_LOW_CONF</t>
-        </is>
-      </c>
+        <v>0.981</v>
+      </c>
+      <c r="J164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -6219,22 +6219,17 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C165" t="inlineStr"/>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>signature_processed</t>
-        </is>
-      </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Bearbeitet</t>
+          <t>Oven A Anlagen-nummer</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>10.06.2026 / ohp</t>
+          <t>A4658</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -6243,7 +6238,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>0.981</v>
+        <v>0.983</v>
       </c>
       <c r="J165" t="inlineStr"/>
     </row>
@@ -6254,33 +6249,32 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C166" t="inlineStr"/>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>signature_checked</t>
-        </is>
-      </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Geprüft</t>
+          <t>Oven A Einsatzbereit gemäß RL-SOP-00796</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>10.06.2026 / hgh</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>auto_accepted</t>
+          <t>needs_review</t>
         </is>
       </c>
       <c r="I166" t="n">
-        <v>0.981</v>
-      </c>
-      <c r="J166" t="inlineStr"/>
+        <v>0.8</v>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>warning:EXTRACT_LOW_CONF</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -6294,12 +6288,12 @@
       <c r="C167" t="inlineStr"/>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Oven A Anlagen-nummer</t>
+          <t>Oven B Anlagen-nummer</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>A4658</t>
+          <t>A3169</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -6324,7 +6318,7 @@
       <c r="C168" t="inlineStr"/>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Oven A Einsatzbereit gemäß RL-SOP-00796</t>
+          <t>Oven B Einsatzbereit gemäß RL-SOP-00796</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -6358,23 +6352,27 @@
       <c r="C169" t="inlineStr"/>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Oven B Anlagen-nummer</t>
+          <t>Oven C Einsatzbereit gemäß RL-SOP-00796</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>A3169</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>auto_accepted</t>
+          <t>needs_review</t>
         </is>
       </c>
       <c r="I169" t="n">
-        <v>0.983</v>
-      </c>
-      <c r="J169" t="inlineStr"/>
+        <v>0.8</v>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>warning:EXTRACT_LOW_CONF</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -6388,7 +6386,7 @@
       <c r="C170" t="inlineStr"/>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Oven B Einsatzbereit gemäß RL-SOP-00796</t>
+          <t>Oven D Einsatzbereit gemäß RL-SOP-00796</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -6420,29 +6418,30 @@
         <v>27</v>
       </c>
       <c r="C171" t="inlineStr"/>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>signature_processed</t>
+        </is>
+      </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Oven C Einsatzbereit gemäß RL-SOP-00796</t>
+          <t>Bearbeitet (Datum/Kürzel)</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>10.06.2026 / oho</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>auto_accepted</t>
         </is>
       </c>
       <c r="I171" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J171" t="inlineStr">
-        <is>
-          <t>warning:EXTRACT_LOW_CONF</t>
-        </is>
-      </c>
+        <v>0.983</v>
+      </c>
+      <c r="J171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -6454,29 +6453,30 @@
         <v>27</v>
       </c>
       <c r="C172" t="inlineStr"/>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>signature_checked</t>
+        </is>
+      </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Oven D Einsatzbereit gemäß RL-SOP-00796</t>
+          <t>Geprüft (Datum/Kürzel)</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>10.06.2026 / hgn</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>auto_accepted</t>
         </is>
       </c>
       <c r="I172" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J172" t="inlineStr">
-        <is>
-          <t>warning:EXTRACT_LOW_CONF</t>
-        </is>
-      </c>
+        <v>0.983</v>
+      </c>
+      <c r="J172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -6485,22 +6485,17 @@
         </is>
       </c>
       <c r="B173" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C173" t="inlineStr"/>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>signature_processed</t>
-        </is>
-      </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Bearbeitet (Datum/Kürzel)</t>
+          <t>Cake Lead Datum (TTMMJJJJ)</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>10.06.2026 / ohr</t>
+          <t>17102025</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -6509,7 +6504,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>0.983</v>
+        <v>1</v>
       </c>
       <c r="J173" t="inlineStr"/>
     </row>
@@ -6520,33 +6515,32 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C174" t="inlineStr"/>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>signature_checked</t>
-        </is>
-      </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Geprüft (Datum/Kürzel)</t>
+          <t>Cake Lead</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>10.06.2026 / hgn</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>auto_accepted</t>
+          <t>needs_review</t>
         </is>
       </c>
       <c r="I174" t="n">
-        <v>0.983</v>
-      </c>
-      <c r="J174" t="inlineStr"/>
+        <v>0.8</v>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>warning:EXTRACT_LOW_CONF</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -6560,23 +6554,32 @@
       <c r="C175" t="inlineStr"/>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Cake Lead - Datum (TTMMJJJJ)</t>
+          <t>Shift Baker</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>17102025</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>mm</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>auto_accepted</t>
+          <t>needs_review</t>
         </is>
       </c>
       <c r="I175" t="n">
-        <v>1</v>
-      </c>
-      <c r="J175" t="inlineStr"/>
+        <v>0.8</v>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>warning:EXTRACT_LOW_CONF</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -6590,7 +6593,7 @@
       <c r="C176" t="inlineStr"/>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Cake Lead</t>
+          <t>Cake Pan BAK B10 angeschlossen als</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -6624,17 +6627,12 @@
       <c r="C177" t="inlineStr"/>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Shift Baker</t>
+          <t>Ofenhandventile BAK B10</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>mm</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -6663,7 +6661,7 @@
       <c r="C178" t="inlineStr"/>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Cake Pan BAK B10 angeschlossen als</t>
+          <t>Cake Pan BAK B30 angeschlossen als</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -6697,7 +6695,7 @@
       <c r="C179" t="inlineStr"/>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Ofenhandventile BAK B10</t>
+          <t>Ofenhandventile BAK B30</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -6731,7 +6729,7 @@
       <c r="C180" t="inlineStr"/>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Cake Pan BAK B30 angeschlossen als</t>
+          <t>Cake Pan BAK B10 angeschlossen als Oven 1</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -6765,7 +6763,7 @@
       <c r="C181" t="inlineStr"/>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Ofenhandventile BAK B30</t>
+          <t>Ofenhandventile BAK B10 Bypass (Position 4-1)</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -6799,7 +6797,7 @@
       <c r="C182" t="inlineStr"/>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Cake Pan BAK B10 angeschlossen als</t>
+          <t>Cake Pan BAK B30 angeschlossen als Oven 1</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -6833,7 +6831,7 @@
       <c r="C183" t="inlineStr"/>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Ofenhandventile BAK B10</t>
+          <t>Ofenhandventile BAK B30 Bypass (Position 4-1)</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -6867,7 +6865,7 @@
       <c r="C184" t="inlineStr"/>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Cake Pan BAK B30 angeschlossen als</t>
+          <t>Cake Pan BAK C45 angeschlossen als Oven 2</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -6901,7 +6899,7 @@
       <c r="C185" t="inlineStr"/>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Ofenhandventile BAK B30</t>
+          <t>Ofenhandventile BAK C45 Bypass (Position 4-1)</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -6935,7 +6933,7 @@
       <c r="C186" t="inlineStr"/>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Cake Pan BAK C45 angeschlossen als</t>
+          <t>Cake Pan BAK B10 angeschlossen als Oven 2</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -6969,7 +6967,7 @@
       <c r="C187" t="inlineStr"/>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Ofenhandventile BAK C45</t>
+          <t>Ofenhandventile BAK B10 Bypass (Position 4-1)</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -7003,7 +7001,7 @@
       <c r="C188" t="inlineStr"/>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Cake Pan BAK B10 angeschlossen als</t>
+          <t>Probenahmestelle am Top Port des Oven Port 2 angekoppelt</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -7035,29 +7033,30 @@
         <v>28</v>
       </c>
       <c r="C189" t="inlineStr"/>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>signature_processed</t>
+        </is>
+      </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Ofenhandventile BAK B10</t>
+          <t>Bearbeitet (Datum/Kürzel)</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>10.06.2026 / ohi</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>auto_accepted</t>
         </is>
       </c>
       <c r="I189" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J189" t="inlineStr">
-        <is>
-          <t>warning:EXTRACT_LOW_CONF</t>
-        </is>
-      </c>
+        <v>0.984</v>
+      </c>
+      <c r="J189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -7069,29 +7068,30 @@
         <v>28</v>
       </c>
       <c r="C190" t="inlineStr"/>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>signature_checked</t>
+        </is>
+      </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Probenahmestelle am Top Port des Oven Port 2 angekoppelt</t>
+          <t>Geprüft (Datum/Kürzel)</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>10.06.2026 / häh</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>auto_accepted</t>
         </is>
       </c>
       <c r="I190" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J190" t="inlineStr">
-        <is>
-          <t>warning:EXTRACT_LOW_CONF</t>
-        </is>
-      </c>
+        <v>0.984</v>
+      </c>
+      <c r="J190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -7100,22 +7100,17 @@
         </is>
       </c>
       <c r="B191" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C191" t="inlineStr"/>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t>signature_processed</t>
-        </is>
-      </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Bearbeitet (Datum/Kürzel)</t>
+          <t>Oven A - Anlagennummer</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>10.06.2026 / ohr</t>
+          <t>A4321</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -7124,7 +7119,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>0.984</v>
+        <v>0.981</v>
       </c>
       <c r="J191" t="inlineStr"/>
     </row>
@@ -7135,33 +7130,32 @@
         </is>
       </c>
       <c r="B192" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C192" t="inlineStr"/>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>signature_checked</t>
-        </is>
-      </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Geprüft (Datum/Kürzel)</t>
+          <t>Oven A - Einsatzbereit gemäß RL-SOP-00796</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>10.06.2026 / häh</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>auto_accepted</t>
+          <t>needs_review</t>
         </is>
       </c>
       <c r="I192" t="n">
-        <v>0.984</v>
-      </c>
-      <c r="J192" t="inlineStr"/>
+        <v>0.8</v>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>warning:EXTRACT_LOW_CONF</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -7173,25 +7167,34 @@
         <v>29</v>
       </c>
       <c r="C193" t="inlineStr"/>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>signature_processed</t>
+        </is>
+      </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Oven A - Anlagennummer</t>
+          <t>Oven A - Bearbeitet (Datum/Kürzel)</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>A4321</t>
+          <t>10.06.2016 / Chp</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>auto_accepted</t>
+          <t>needs_review</t>
         </is>
       </c>
       <c r="I193" t="n">
-        <v>0.981</v>
-      </c>
-      <c r="J193" t="inlineStr"/>
+        <v>0.7</v>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>warning:DATE_BEFORE_PRINT</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -7203,14 +7206,19 @@
         <v>29</v>
       </c>
       <c r="C194" t="inlineStr"/>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>signature_checked</t>
+        </is>
+      </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Oven A - Einsatzbereit gemäß RL-SOP-00796</t>
+          <t>Oven A - Geprüft (Datum/Kürzel)</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>10.06.2016 / haa</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -7219,11 +7227,11 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>warning:EXTRACT_LOW_CONF</t>
+          <t>warning:DATE_BEFORE_PRINT</t>
         </is>
       </c>
     </row>
@@ -7301,25 +7309,34 @@
         <v>29</v>
       </c>
       <c r="C197" t="inlineStr"/>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>signature_processed</t>
+        </is>
+      </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Floor Scale - Anlagennummer</t>
+          <t>Mixing Bowl - Bearbeitet (Datum/Kürzel)</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>A9726</t>
+          <t>10.06.2016 / Chp</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>auto_accepted</t>
+          <t>needs_review</t>
         </is>
       </c>
       <c r="I197" t="n">
-        <v>0.981</v>
-      </c>
-      <c r="J197" t="inlineStr"/>
+        <v>0.7</v>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>warning:DATE_BEFORE_PRINT</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -7331,14 +7348,19 @@
         <v>29</v>
       </c>
       <c r="C198" t="inlineStr"/>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>signature_checked</t>
+        </is>
+      </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Floor Scale - Einsatzbereit gemäß RL-SOP-00796</t>
+          <t>Mixing Bowl - Geprüft (Datum/Kürzel)</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>10.06.2016 / haa</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -7347,11 +7369,11 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>warning:EXTRACT_LOW_CONF</t>
+          <t>warning:DATE_BEFORE_PRINT</t>
         </is>
       </c>
     </row>
@@ -7365,34 +7387,25 @@
         <v>29</v>
       </c>
       <c r="C199" t="inlineStr"/>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t>signature_processed</t>
-        </is>
-      </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Bearbeitet (Datum/Kürzel)</t>
+          <t>Floor Scale - Anlagennummer</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>10.06.2016 / Ohp</t>
+          <t>A9726</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>auto_accepted</t>
         </is>
       </c>
       <c r="I199" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J199" t="inlineStr">
-        <is>
-          <t>warning:EXTRACT_LOW_CONF</t>
-        </is>
-      </c>
+        <v>0.981</v>
+      </c>
+      <c r="J199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -7404,19 +7417,14 @@
         <v>29</v>
       </c>
       <c r="C200" t="inlineStr"/>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t>signature_checked</t>
-        </is>
-      </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Geprüft (Datum/Kürzel)</t>
+          <t>Floor Scale - Einsatzbereit gemäß RL-SOP-00796</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>10.06.2016 / haa</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -7445,7 +7453,7 @@
       <c r="C201" t="inlineStr"/>
       <c r="E201" t="inlineStr">
         <is>
-          <t>B20-PP 57497</t>
+          <t>Intermediat B20-PP 57497</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -7480,7 +7488,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>BK-MIX-88-FXF – BK-SOP-40918 geprüft</t>
+          <t>BK-MIX-88-FXF - BK-SOP-40918 geprüft</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -7494,11 +7502,11 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>error:FMT_DATE_PADDING</t>
+          <t>warning:EXTRACT_LOW_CONF</t>
         </is>
       </c>
     </row>
@@ -7519,7 +7527,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>BK-MIX-65-FXF – BK-SOP-40918 geprüft</t>
+          <t>BK-MIX-65-FXF - BK-SOP-40918 geprüft</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -7533,11 +7541,11 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>error:FMT_DATE_PADDING</t>
+          <t>warning:EXTRACT_LOW_CONF</t>
         </is>
       </c>
     </row>
@@ -7558,7 +7566,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>BK-MIX-30-FXF – BK-SOP-40918 geprüft</t>
+          <t>BK-MIX-30-FXF - BK-SOP-40918 geprüft</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -7572,11 +7580,11 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>error:FMT_DATE_PADDING</t>
+          <t>warning:EXTRACT_LOW_CONF</t>
         </is>
       </c>
     </row>
@@ -7770,7 +7778,7 @@
       <c r="C210" t="inlineStr"/>
       <c r="E210" t="inlineStr">
         <is>
-          <t>SAP gebucht Ja</t>
+          <t>SAP gebucht</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -7848,7 +7856,7 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>10.06.2026 /</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -7908,7 +7916,7 @@
       <c r="C214" t="inlineStr"/>
       <c r="E214" t="inlineStr">
         <is>
-          <t>SAP gebucht Ja</t>
+          <t>SAP gebucht</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -7986,7 +7994,7 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>10.06.2026 /</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -8046,7 +8054,7 @@
       <c r="C218" t="inlineStr"/>
       <c r="E218" t="inlineStr">
         <is>
-          <t>SAP gebucht Ja</t>
+          <t>SAP gebucht</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -8260,7 +8268,7 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>10.06.2026 / ohp</t>
+          <t>10.06.2026 / obp</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -8299,7 +8307,7 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>10.06.2026 / ohp</t>
+          <t>10.06.2026 / obp</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -8406,7 +8414,7 @@
       <c r="C228" t="inlineStr"/>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Cream Blend 859 Flavor Mix BAG 280 L / Material Nr. 2839719 - Anzahl gekoppelter Puffergebinde</t>
+          <t>Cream Blend 859 Flavor Mix BAG 280 L - Anzahl gekoppelter Puffergebinde (Material Nr. 2839719)</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
@@ -8445,7 +8453,7 @@
       <c r="C229" t="inlineStr"/>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Cream Blend 859 Flavor Mix BAG 280 L / Material Nr. 1057404 - Anzahl gekoppelter Puffergebinde</t>
+          <t>Cream Blend 859 Flavor Mix BAG 280 L - Anzahl gekoppelter Puffergebinde (Material Nr. 1057404)</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -8533,7 +8541,7 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>10.06.2026 / ohe</t>
+          <t>10.06.2026 / ohp</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -8568,7 +8576,7 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>10.06.2026 / ohe</t>
+          <t>10.06.2026 / ohp</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -8850,12 +8858,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Bearbeitet (Datum/Kürzel)</t>
+          <t>Bearbeitet</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>10.06.2026 / ohr</t>
+          <t>10.06.2026 / ohp</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -8885,12 +8893,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Geprüft (Datum/Kürzel)</t>
+          <t>Geprüft</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>10.06.2026 / ohr</t>
+          <t>10.06.2026 / ohp</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -9026,7 +9034,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Erlaubte Standzeit</t>
+          <t>Erlaubte Standzeit (≤ 82 h.)</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -9066,12 +9074,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Bearbeitet (Datum/Kürzel)</t>
+          <t>Bearbeitet</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>10.06.2026 / ohr</t>
+          <t>10.06.2026 / ohp</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -9101,12 +9109,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Geprüft (Datum/Kürzel)</t>
+          <t>Geprüft</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>10.06.2026 / ohr</t>
+          <t>10.06.2026 / ohp</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -9338,17 +9346,17 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Dauer Auftrag Minuten</t>
+          <t>Dauer Auftrag Stunden</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>min</t>
+          <t>h</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -9357,7 +9365,7 @@
         </is>
       </c>
       <c r="I253" t="n">
-        <v>0.958</v>
+        <v>0.948</v>
       </c>
       <c r="J253" t="inlineStr"/>
     </row>
@@ -9373,33 +9381,37 @@
       <c r="C254" t="inlineStr"/>
       <c r="D254" t="inlineStr">
         <is>
-          <t>hold_duration</t>
+          <t>volume</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Dauer Auftrag Stunden</t>
+          <t>Load Volumen</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>293.78</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>L</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>auto_accepted</t>
+          <t>needs_review</t>
         </is>
       </c>
       <c r="I254" t="n">
-        <v>0.948</v>
-      </c>
-      <c r="J254" t="inlineStr"/>
+        <v>0.8</v>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>warning:EXTRACT_LOW_CONF</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -9413,22 +9425,17 @@
       <c r="C255" t="inlineStr"/>
       <c r="D255" t="inlineStr">
         <is>
-          <t>volume</t>
+          <t>signature_processed</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Load Volumen - Mittlerer Fluss vor Ofen</t>
+          <t>Bearbeitet</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>6.6</t>
-        </is>
-      </c>
-      <c r="G255" t="inlineStr">
-        <is>
-          <t>l/h</t>
+          <t>10.06.2026 / o4e</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -9457,33 +9464,32 @@
       <c r="C256" t="inlineStr"/>
       <c r="D256" t="inlineStr">
         <is>
-          <t>hold_duration</t>
+          <t>signature_checked</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Load Volumen - Dauer Auftrag Stunden</t>
+          <t>Geprüft</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="G256" t="inlineStr">
-        <is>
-          <t>h</t>
+          <t>10.06.2026 / o4e</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>auto_accepted</t>
+          <t>needs_review</t>
         </is>
       </c>
       <c r="I256" t="n">
-        <v>0.958</v>
-      </c>
-      <c r="J256" t="inlineStr"/>
+        <v>0.4</v>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>error:4EYES_DISTINCT</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -9492,42 +9498,33 @@
         </is>
       </c>
       <c r="B257" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C257" t="inlineStr"/>
-      <c r="D257" t="inlineStr">
-        <is>
-          <t>volume</t>
-        </is>
-      </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Load Volumen - Mittlerer Fluss Pumpe A</t>
+          <t>m B20-ST</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>327</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>l/h</t>
+          <t>g</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>auto_accepted</t>
         </is>
       </c>
       <c r="I257" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J257" t="inlineStr">
-        <is>
-          <t>warning:EXTRACT_LOW_CONF</t>
-        </is>
-      </c>
+        <v>0.989</v>
+      </c>
+      <c r="J257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -9536,38 +9533,42 @@
         </is>
       </c>
       <c r="B258" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C258" t="inlineStr"/>
       <c r="D258" t="inlineStr">
         <is>
-          <t>hold_duration</t>
+          <t>volume</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Load Volumen - Dauer Auftrag Stunden</t>
+          <t>V B20-ST Netto nPz</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>314</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>L</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>auto_accepted</t>
+          <t>needs_review</t>
         </is>
       </c>
       <c r="I258" t="n">
-        <v>0.948</v>
-      </c>
-      <c r="J258" t="inlineStr"/>
+        <v>0.8</v>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>warning:EXTRACT_LOW_CONF</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -9576,38 +9577,42 @@
         </is>
       </c>
       <c r="B259" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C259" t="inlineStr"/>
       <c r="D259" t="inlineStr">
         <is>
-          <t>volume</t>
+          <t>concentration</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Load Volumen</t>
+          <t>C B20-ST Cake</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>2021.78</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>g/L</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>auto_accepted</t>
+          <t>needs_review</t>
         </is>
       </c>
       <c r="I259" t="n">
-        <v>0.951</v>
-      </c>
-      <c r="J259" t="inlineStr"/>
+        <v>0.8</v>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>warning:EXTRACT_LOW_CONF</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -9616,22 +9621,27 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C260" t="inlineStr"/>
       <c r="D260" t="inlineStr">
         <is>
-          <t>signature_processed</t>
+          <t>volume</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Bearbeitet</t>
+          <t>V Loadvolumen</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>10.06.2026 / ole</t>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -9640,7 +9650,7 @@
         </is>
       </c>
       <c r="I260" t="n">
-        <v>0.953</v>
+        <v>0.989</v>
       </c>
       <c r="J260" t="inlineStr"/>
     </row>
@@ -9651,22 +9661,27 @@
         </is>
       </c>
       <c r="B261" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C261" t="inlineStr"/>
       <c r="D261" t="inlineStr">
         <is>
-          <t>signature_checked</t>
+          <t>concentration</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Geprüft</t>
+          <t>C B20-ST Cake</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>10.06.2026 / ole</t>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>g/L</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -9675,11 +9690,11 @@
         </is>
       </c>
       <c r="I261" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>error:4EYES_DISTINCT</t>
+          <t>warning:EXTRACT_LOW_CONF</t>
         </is>
       </c>
     </row>
@@ -9693,30 +9708,39 @@
         <v>37</v>
       </c>
       <c r="C262" t="inlineStr"/>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>volume</t>
+        </is>
+      </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>m B20-ST</t>
+          <t>V Ofen BAK B20</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>327</t>
+          <t>50</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>L</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>auto_accepted</t>
+          <t>needs_review</t>
         </is>
       </c>
       <c r="I262" t="n">
-        <v>0.989</v>
-      </c>
-      <c r="J262" t="inlineStr"/>
+        <v>0.8</v>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>warning:EXTRACT_LOW_CONF</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -9728,35 +9752,34 @@
         <v>37</v>
       </c>
       <c r="C263" t="inlineStr"/>
-      <c r="D263" t="inlineStr">
-        <is>
-          <t>volume</t>
-        </is>
-      </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>V B20-ST Netto nPz</t>
+          <t>Beladung</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>g Cake /LMilk</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>auto_accepted</t>
+          <t>needs_review</t>
         </is>
       </c>
       <c r="I263" t="n">
-        <v>0.989</v>
-      </c>
-      <c r="J263" t="inlineStr"/>
+        <v>0.4</v>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>error:RANGE_SOLL</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -9768,24 +9791,14 @@
         <v>37</v>
       </c>
       <c r="C264" t="inlineStr"/>
-      <c r="D264" t="inlineStr">
-        <is>
-          <t>concentration</t>
-        </is>
-      </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>C B20-ST Cake</t>
+          <t>Beladung 7–19 g Cake /LMilk eingehalten</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G264" t="inlineStr">
-        <is>
-          <t>g/L</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -9814,22 +9827,17 @@
       <c r="C265" t="inlineStr"/>
       <c r="D265" t="inlineStr">
         <is>
-          <t>volume</t>
+          <t>signature_processed</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>V Loadvolumen</t>
+          <t>Bearbeitet</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="G265" t="inlineStr">
-        <is>
-          <t>L</t>
+          <t>10.06.2026 / oho</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -9838,7 +9846,7 @@
         </is>
       </c>
       <c r="I265" t="n">
-        <v>0.989</v>
+        <v>0.99</v>
       </c>
       <c r="J265" t="inlineStr"/>
     </row>
@@ -9854,22 +9862,17 @@
       <c r="C266" t="inlineStr"/>
       <c r="D266" t="inlineStr">
         <is>
-          <t>concentration</t>
+          <t>signature_checked</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>C B20-ST Cake</t>
+          <t>Geprüft</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>2.1</t>
-        </is>
-      </c>
-      <c r="G266" t="inlineStr">
-        <is>
-          <t>g/L</t>
+          <t>10.06.2026 / oho</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -9878,11 +9881,11 @@
         </is>
       </c>
       <c r="I266" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>warning:EXTRACT_LOW_CONF</t>
+          <t>error:4EYES_DISTINCT</t>
         </is>
       </c>
     </row>
@@ -9893,42 +9896,38 @@
         </is>
       </c>
       <c r="B267" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C267" t="inlineStr"/>
       <c r="D267" t="inlineStr">
         <is>
-          <t>volume</t>
+          <t>hold_start</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>V Ofen BAK B20</t>
+          <t>Start Haltezeit (Übertrag Kapitel 5.3.1)</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>2026-06-09T08:27:00</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>Uhr</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>auto_accepted</t>
         </is>
       </c>
       <c r="I267" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J267" t="inlineStr">
-        <is>
-          <t>warning:EXTRACT_LOW_CONF</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="J267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -9937,37 +9936,38 @@
         </is>
       </c>
       <c r="B268" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C268" t="inlineStr"/>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>hold_end</t>
+        </is>
+      </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Beladung</t>
+          <t>Ende Haltezeit (Übertrag Kapitel 5.12.1)</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2026-06-10T10:14:00</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>g Cake /LMilk</t>
+          <t>Uhr</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>auto_accepted</t>
         </is>
       </c>
       <c r="I268" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J268" t="inlineStr">
-        <is>
-          <t>warning:EXTRACT_LOW_CONF</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="J268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -9976,17 +9976,22 @@
         </is>
       </c>
       <c r="B269" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C269" t="inlineStr"/>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Beladung 7–19 g Cake /LMilk eingehalten</t>
+          <t>Tatsächliche Haltezeit</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>h</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -10010,33 +10015,32 @@
         </is>
       </c>
       <c r="B270" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C270" t="inlineStr"/>
-      <c r="D270" t="inlineStr">
-        <is>
-          <t>signature_processed</t>
-        </is>
-      </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Bearbeitet</t>
+          <t>B10-PP aus Zyklus 2 eingesetzt</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>10.06.2026 / ohp</t>
+          <t>Nein, Feld findet keine Anwendung</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>auto_accepted</t>
+          <t>needs_review</t>
         </is>
       </c>
       <c r="I270" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="J270" t="inlineStr"/>
+        <v>0.8</v>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>warning:EXTRACT_LOW_CONF</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -10045,22 +10049,27 @@
         </is>
       </c>
       <c r="B271" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C271" t="inlineStr"/>
       <c r="D271" t="inlineStr">
         <is>
-          <t>signature_checked</t>
+          <t>hold_start</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Geprüft</t>
+          <t>Start Haltezeit (Übertrag Kapitel 5.3.2)</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>10.06.2026 / ohp</t>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>Uhr</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -10069,11 +10078,11 @@
         </is>
       </c>
       <c r="I271" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>error:4EYES_DISTINCT</t>
+          <t>warning:EXTRACT_LOW_CONF</t>
         </is>
       </c>
     </row>
@@ -10089,17 +10098,17 @@
       <c r="C272" t="inlineStr"/>
       <c r="D272" t="inlineStr">
         <is>
-          <t>hold_start</t>
+          <t>hold_end</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Start Haltezeit (Übertrag Kapitel 5.3.1)</t>
+          <t>Ende Haltezeit (Übertrag Kapitel 5.12.1)</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>2016-06-09T08:27:00</t>
+          <t>/</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
@@ -10133,37 +10142,28 @@
       <c r="C273" t="inlineStr"/>
       <c r="D273" t="inlineStr">
         <is>
-          <t>hold_end</t>
+          <t>signature_processed</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Ende Haltezeit (Übertrag Kapitel 5.12.1)</t>
+          <t>Bearbeitet</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>2016-06-10T10:14:00</t>
-        </is>
-      </c>
-      <c r="G273" t="inlineStr">
-        <is>
-          <t>Uhr</t>
+          <t>10.06.2026 / oh</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>auto_accepted</t>
         </is>
       </c>
       <c r="I273" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J273" t="inlineStr">
-        <is>
-          <t>warning:EXTRACT_LOW_CONF</t>
-        </is>
-      </c>
+        <v>0.957</v>
+      </c>
+      <c r="J273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -10175,19 +10175,19 @@
         <v>38</v>
       </c>
       <c r="C274" t="inlineStr"/>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>signature_checked</t>
+        </is>
+      </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Tatsächliche Haltezeit</t>
+          <t>Geprüft</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="G274" t="inlineStr">
-        <is>
-          <t>h</t>
+          <t>10.06.2026 / oh</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -10196,11 +10196,11 @@
         </is>
       </c>
       <c r="I274" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>warning:EXTRACT_LOW_CONF</t>
+          <t>error:4EYES_DISTINCT</t>
         </is>
       </c>
     </row>
@@ -10211,32 +10211,38 @@
         </is>
       </c>
       <c r="B275" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C275" t="inlineStr"/>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>hold_start</t>
+        </is>
+      </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>B10-PP aus Zyklus 2 eingesetzt</t>
+          <t>Start Temperierung (Übertrag Kapitel 5.4.1)</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Nein, Feld findet keine Anwendung</t>
+          <t>2026-06-10T14:27:00</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>Uhr</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>auto_accepted</t>
         </is>
       </c>
       <c r="I275" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J275" t="inlineStr">
-        <is>
-          <t>warning:EXTRACT_LOW_CONF</t>
-        </is>
-      </c>
+        <v>0.996</v>
+      </c>
+      <c r="J275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -10245,37 +10251,38 @@
         </is>
       </c>
       <c r="B276" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C276" t="inlineStr"/>
       <c r="D276" t="inlineStr">
         <is>
-          <t>signature_processed</t>
+          <t>hold_end</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Bearbeitet</t>
+          <t>Ende Temperierung (Übertrag Kapitel 5.12.1)</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>10.06.2016 / dhr</t>
+          <t>2026-06-10T16:14:00</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>Uhr</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>auto_accepted</t>
         </is>
       </c>
       <c r="I276" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J276" t="inlineStr">
-        <is>
-          <t>warning:EXTRACT_LOW_CONF</t>
-        </is>
-      </c>
+        <v>0.996</v>
+      </c>
+      <c r="J276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -10284,22 +10291,27 @@
         </is>
       </c>
       <c r="B277" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C277" t="inlineStr"/>
       <c r="D277" t="inlineStr">
         <is>
-          <t>signature_checked</t>
+          <t>hold_duration</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Geprüft</t>
+          <t>Dauer Temperierung</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>10.06.2016 / dhr</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>h</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -10312,7 +10324,7 @@
       </c>
       <c r="J277" t="inlineStr">
         <is>
-          <t>error:4EYES_DISTINCT</t>
+          <t>error:RANGE_SOLL</t>
         </is>
       </c>
     </row>
@@ -10326,35 +10338,29 @@
         <v>39</v>
       </c>
       <c r="C278" t="inlineStr"/>
-      <c r="D278" t="inlineStr">
-        <is>
-          <t>hold_start</t>
-        </is>
-      </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Start Temperierung (Übertrag Kapitel 5.4.1)</t>
+          <t>B10-PP aus Zyklus 2 eingesetzt</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>2026-06-10T14:27:00</t>
-        </is>
-      </c>
-      <c r="G278" t="inlineStr">
-        <is>
-          <t>Uhr</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>auto_accepted</t>
+          <t>needs_review</t>
         </is>
       </c>
       <c r="I278" t="n">
-        <v>0.996</v>
-      </c>
-      <c r="J278" t="inlineStr"/>
+        <v>0.8</v>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>warning:EXTRACT_LOW_CONF</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -10366,35 +10372,29 @@
         <v>39</v>
       </c>
       <c r="C279" t="inlineStr"/>
-      <c r="D279" t="inlineStr">
-        <is>
-          <t>hold_end</t>
-        </is>
-      </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Ende Temperierung (Übertrag Kapitel 5.12.1)</t>
+          <t>Temperierung durchgeführt</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>2026-06-10T16:14:00</t>
-        </is>
-      </c>
-      <c r="G279" t="inlineStr">
-        <is>
-          <t>Uhr</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>auto_accepted</t>
+          <t>needs_review</t>
         </is>
       </c>
       <c r="I279" t="n">
-        <v>0.996</v>
-      </c>
-      <c r="J279" t="inlineStr"/>
+        <v>0.8</v>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>warning:EXTRACT_LOW_CONF</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -10408,37 +10408,33 @@
       <c r="C280" t="inlineStr"/>
       <c r="D280" t="inlineStr">
         <is>
-          <t>hold_duration</t>
+          <t>hold_start</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Dauer Temperierung</t>
+          <t>Start Temperierung (Übertrag Kapitel 5.5.1)</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2026-06-10T17:12:00</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>Uhr</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>auto_accepted</t>
         </is>
       </c>
       <c r="I280" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J280" t="inlineStr">
-        <is>
-          <t>error:RANGE_SOLL</t>
-        </is>
-      </c>
+        <v>0.996</v>
+      </c>
+      <c r="J280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -10450,29 +10446,35 @@
         <v>39</v>
       </c>
       <c r="C281" t="inlineStr"/>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>hold_end</t>
+        </is>
+      </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>B10-PP aus Zyklus 2 eingesetzt</t>
+          <t>Ende Temperierung (Übertrag Kapitel 5.12.1)</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>2026-06-10T19:24:00</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>Uhr</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>auto_accepted</t>
         </is>
       </c>
       <c r="I281" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J281" t="inlineStr">
-        <is>
-          <t>warning:EXTRACT_LOW_CONF</t>
-        </is>
-      </c>
+        <v>0.996</v>
+      </c>
+      <c r="J281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -10484,14 +10486,24 @@
         <v>39</v>
       </c>
       <c r="C282" t="inlineStr"/>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>hold_duration</t>
+        </is>
+      </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Temperierung durchgeführt</t>
+          <t>Dauer Temperierung</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>h</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -10500,11 +10512,11 @@
         </is>
       </c>
       <c r="I282" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>warning:EXTRACT_LOW_CONF</t>
+          <t>error:RANGE_SOLL</t>
         </is>
       </c>
     </row>
@@ -10520,22 +10532,17 @@
       <c r="C283" t="inlineStr"/>
       <c r="D283" t="inlineStr">
         <is>
-          <t>hold_start</t>
+          <t>signature_processed</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Start Temperierung (Übertrag Kapitel 5.5.1)</t>
+          <t>Bearbeitet</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>2026-06-10T17:12:00</t>
-        </is>
-      </c>
-      <c r="G283" t="inlineStr">
-        <is>
-          <t>Uhr</t>
+          <t>10.06.2026 / ohr</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -10544,7 +10551,7 @@
         </is>
       </c>
       <c r="I283" t="n">
-        <v>0.996</v>
+        <v>0.979</v>
       </c>
       <c r="J283" t="inlineStr"/>
     </row>
@@ -10560,33 +10567,32 @@
       <c r="C284" t="inlineStr"/>
       <c r="D284" t="inlineStr">
         <is>
-          <t>hold_end</t>
+          <t>signature_checked</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Ende Temperierung (Übertrag Kapitel 5.12.1)</t>
+          <t>Geprüft</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>2026-06-10T19:24:00</t>
-        </is>
-      </c>
-      <c r="G284" t="inlineStr">
-        <is>
-          <t>Uhr</t>
+          <t>10.06.2026 / ohr</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>auto_accepted</t>
+          <t>needs_review</t>
         </is>
       </c>
       <c r="I284" t="n">
-        <v>0.996</v>
-      </c>
-      <c r="J284" t="inlineStr"/>
+        <v>0.4</v>
+      </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>error:4EYES_DISTINCT</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -10595,42 +10601,28 @@
         </is>
       </c>
       <c r="B285" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C285" t="inlineStr"/>
-      <c r="D285" t="inlineStr">
-        <is>
-          <t>hold_duration</t>
-        </is>
-      </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Dauer Temperierung</t>
+          <t>Intermediat</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G285" t="inlineStr">
-        <is>
-          <t>h</t>
+          <t>241</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>auto_accepted</t>
         </is>
       </c>
       <c r="I285" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J285" t="inlineStr">
-        <is>
-          <t>error:RANGE_SOLL</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="J285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -10639,22 +10631,27 @@
         </is>
       </c>
       <c r="B286" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C286" t="inlineStr"/>
       <c r="D286" t="inlineStr">
         <is>
-          <t>signature_processed</t>
+          <t>tare_mass</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Bearbeitet: (Datum/Kürzel)</t>
+          <t>m Tara</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>10.06.2026 / ohe</t>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>kg</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -10663,7 +10660,7 @@
         </is>
       </c>
       <c r="I286" t="n">
-        <v>0.979</v>
+        <v>0.999</v>
       </c>
       <c r="J286" t="inlineStr"/>
     </row>
@@ -10674,22 +10671,27 @@
         </is>
       </c>
       <c r="B287" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C287" t="inlineStr"/>
       <c r="D287" t="inlineStr">
         <is>
-          <t>signature_checked</t>
+          <t>gross_mass</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Geprüft: (Datum/Kürzel)</t>
+          <t>m Brutto vPZ</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>10.06.2026 / ohr</t>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>kg</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -10698,7 +10700,7 @@
         </is>
       </c>
       <c r="I287" t="n">
-        <v>0.979</v>
+        <v>1</v>
       </c>
       <c r="J287" t="inlineStr"/>
     </row>
@@ -10712,14 +10714,24 @@
         <v>40</v>
       </c>
       <c r="C288" t="inlineStr"/>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>net_mass</t>
+        </is>
+      </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Intermediat</t>
+          <t>m Netto vPZ</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>kg</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -10744,22 +10756,22 @@
       <c r="C289" t="inlineStr"/>
       <c r="D289" t="inlineStr">
         <is>
-          <t>tare_mass</t>
+          <t>volume</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>m Tara</t>
+          <t>V Netto vPZ</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>236</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>L</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -10768,7 +10780,7 @@
         </is>
       </c>
       <c r="I289" t="n">
-        <v>0.999</v>
+        <v>1</v>
       </c>
       <c r="J289" t="inlineStr"/>
     </row>
@@ -10782,35 +10794,29 @@
         <v>40</v>
       </c>
       <c r="C290" t="inlineStr"/>
-      <c r="D290" t="inlineStr">
-        <is>
-          <t>gross_mass</t>
-        </is>
-      </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>m Brutto vPZ</t>
+          <t>Proben (QC) erforderlich</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="G290" t="inlineStr">
-        <is>
-          <t>kg</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>auto_accepted</t>
+          <t>needs_review</t>
         </is>
       </c>
       <c r="I290" t="n">
-        <v>1</v>
-      </c>
-      <c r="J290" t="inlineStr"/>
+        <v>0.8</v>
+      </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>warning:EXTRACT_LOW_CONF</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -10822,35 +10828,29 @@
         <v>40</v>
       </c>
       <c r="C291" t="inlineStr"/>
-      <c r="D291" t="inlineStr">
-        <is>
-          <t>net_mass</t>
-        </is>
-      </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>m Netto vPZ</t>
+          <t>Proben gemäß Sonderprobenzugplan erforderlich</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="G291" t="inlineStr">
-        <is>
-          <t>kg</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>auto_accepted</t>
+          <t>needs_review</t>
         </is>
       </c>
       <c r="I291" t="n">
-        <v>1</v>
-      </c>
-      <c r="J291" t="inlineStr"/>
+        <v>0.8</v>
+      </c>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t>warning:EXTRACT_LOW_CONF</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -10864,22 +10864,22 @@
       <c r="C292" t="inlineStr"/>
       <c r="D292" t="inlineStr">
         <is>
-          <t>volume</t>
+          <t>gross_mass</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>V Netto vPZ</t>
+          <t>m Brutto nPZ</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>100</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -10888,7 +10888,7 @@
         </is>
       </c>
       <c r="I292" t="n">
-        <v>1</v>
+        <v>0.999</v>
       </c>
       <c r="J292" t="inlineStr"/>
     </row>
@@ -10902,29 +10902,35 @@
         <v>40</v>
       </c>
       <c r="C293" t="inlineStr"/>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>net_mass</t>
+        </is>
+      </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Proben (QC) erforderlich</t>
+          <t>m Netto nPZ</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>kg</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>auto_accepted</t>
         </is>
       </c>
       <c r="I293" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J293" t="inlineStr">
-        <is>
-          <t>warning:EXTRACT_LOW_CONF</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="J293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -10936,14 +10942,24 @@
         <v>40</v>
       </c>
       <c r="C294" t="inlineStr"/>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>volume</t>
+        </is>
+      </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Proben gemäß Sonderprobenzugplan erforderlich</t>
+          <t>V Netto nPZ</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -10952,11 +10968,11 @@
         </is>
       </c>
       <c r="I294" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>warning:EXTRACT_LOW_CONF</t>
+          <t>error:CALC_FORMULA</t>
         </is>
       </c>
     </row>
@@ -10972,22 +10988,17 @@
       <c r="C295" t="inlineStr"/>
       <c r="D295" t="inlineStr">
         <is>
-          <t>gross_mass</t>
+          <t>signature_processed</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>m Brutto nPZ</t>
+          <t>Bearbeitet</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="G295" t="inlineStr">
-        <is>
-          <t>kg</t>
+          <t>10.06.2026 / olp</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -10996,7 +11007,7 @@
         </is>
       </c>
       <c r="I295" t="n">
-        <v>0.999</v>
+        <v>0.998</v>
       </c>
       <c r="J295" t="inlineStr"/>
     </row>
@@ -11012,33 +11023,32 @@
       <c r="C296" t="inlineStr"/>
       <c r="D296" t="inlineStr">
         <is>
-          <t>net_mass</t>
+          <t>signature_checked</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>m Netto nPZ</t>
+          <t>Geprüft</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="G296" t="inlineStr">
-        <is>
-          <t>kg</t>
+          <t>10.06.2026 / olp</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>auto_accepted</t>
+          <t>needs_review</t>
         </is>
       </c>
       <c r="I296" t="n">
-        <v>1</v>
-      </c>
-      <c r="J296" t="inlineStr"/>
+        <v>0.4</v>
+      </c>
+      <c r="J296" t="inlineStr">
+        <is>
+          <t>error:4EYES_DISTINCT</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -11050,24 +11060,19 @@
         <v>40</v>
       </c>
       <c r="C297" t="inlineStr"/>
-      <c r="D297" t="inlineStr">
-        <is>
-          <t>volume</t>
-        </is>
-      </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>V Netto nPZ</t>
+          <t>Baker Nine</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>437</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>mAU</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -11090,19 +11095,19 @@
         <v>40</v>
       </c>
       <c r="C298" t="inlineStr"/>
-      <c r="D298" t="inlineStr">
-        <is>
-          <t>signature_processed</t>
-        </is>
-      </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Bearbeitet</t>
+          <t>Browning Point 3 (Anstieg)</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>10.06.2026 / dhp</t>
+          <t>1046</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>mAU</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -11111,7 +11116,7 @@
         </is>
       </c>
       <c r="I298" t="n">
-        <v>0.998</v>
+        <v>1</v>
       </c>
       <c r="J298" t="inlineStr"/>
     </row>
@@ -11125,19 +11130,19 @@
         <v>40</v>
       </c>
       <c r="C299" t="inlineStr"/>
-      <c r="D299" t="inlineStr">
-        <is>
-          <t>signature_checked</t>
-        </is>
-      </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Geprüft</t>
+          <t>Cake Lead</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>10.06.2026 / dhp</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>mAU</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -11146,11 +11151,11 @@
         </is>
       </c>
       <c r="I299" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J299" t="inlineStr">
         <is>
-          <t>error:4EYES_DISTINCT</t>
+          <t>warning:EXTRACT_LOW_CONF</t>
         </is>
       </c>
     </row>
@@ -11166,12 +11171,12 @@
       <c r="C300" t="inlineStr"/>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Baker Nine</t>
+          <t>Browning Point 7 (Abstieg)</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>437</t>
+          <t>327</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
@@ -11196,22 +11201,22 @@
         </is>
       </c>
       <c r="B301" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C301" t="inlineStr"/>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>signature_processed</t>
+        </is>
+      </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Browning Point 3 (Anstieg)</t>
+          <t>Bearbeitet: (Datum/Kürzel)</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>1046</t>
-        </is>
-      </c>
-      <c r="G301" t="inlineStr">
-        <is>
-          <t>mAU</t>
+          <t>10.06.2026 / ohp</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -11220,7 +11225,7 @@
         </is>
       </c>
       <c r="I301" t="n">
-        <v>1</v>
+        <v>0.951</v>
       </c>
       <c r="J301" t="inlineStr"/>
     </row>
@@ -11231,22 +11236,22 @@
         </is>
       </c>
       <c r="B302" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C302" t="inlineStr"/>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>signature_checked</t>
+        </is>
+      </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Cake Lead</t>
+          <t>Geprüft: (Datum/Kürzel)</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="G302" t="inlineStr">
-        <is>
-          <t>mAU</t>
+          <t>10.06.2026 / ohp</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -11255,11 +11260,11 @@
         </is>
       </c>
       <c r="I302" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J302" t="inlineStr">
         <is>
-          <t>warning:EXTRACT_LOW_CONF</t>
+          <t>error:4EYES_DISTINCT</t>
         </is>
       </c>
     </row>
@@ -11270,22 +11275,22 @@
         </is>
       </c>
       <c r="B303" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C303" t="inlineStr"/>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Browning Point 7 (Abstieg)</t>
+          <t>Probenzug</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>327</t>
+          <t>2026-06-10T08:14:00</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>mAU</t>
+          <t>Uhr</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -11294,7 +11299,7 @@
         </is>
       </c>
       <c r="I303" t="n">
-        <v>1</v>
+        <v>0.983</v>
       </c>
       <c r="J303" t="inlineStr"/>
     </row>
@@ -11308,30 +11313,29 @@
         <v>41</v>
       </c>
       <c r="C304" t="inlineStr"/>
-      <c r="D304" t="inlineStr">
-        <is>
-          <t>signature_processed</t>
-        </is>
-      </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Bearbeitet</t>
+          <t>Probenzugsetikett(en) auf Probe(n) mit eingeklebtem(n) Etikett(en) identisch</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>10.06.2026 / ohp</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>auto_accepted</t>
+          <t>needs_review</t>
         </is>
       </c>
       <c r="I304" t="n">
-        <v>0.951</v>
-      </c>
-      <c r="J304" t="inlineStr"/>
+        <v>0.8</v>
+      </c>
+      <c r="J304" t="inlineStr">
+        <is>
+          <t>warning:EXTRACT_LOW_CONF</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -11343,30 +11347,29 @@
         <v>41</v>
       </c>
       <c r="C305" t="inlineStr"/>
-      <c r="D305" t="inlineStr">
-        <is>
-          <t>signature_checked</t>
-        </is>
-      </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Geprüft</t>
+          <t>Stage Etikett und Probenzugsetikett(en) in LIMS received, sowie Lagerort (03er Proben Lagerort = „in Bearbeitung“) angegeben</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>10.06.2026 / ohe</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>auto_accepted</t>
+          <t>needs_review</t>
         </is>
       </c>
       <c r="I305" t="n">
-        <v>0.951</v>
-      </c>
-      <c r="J305" t="inlineStr"/>
+        <v>0.8</v>
+      </c>
+      <c r="J305" t="inlineStr">
+        <is>
+          <t>warning:EXTRACT_LOW_CONF</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -11380,17 +11383,12 @@
       <c r="C306" t="inlineStr"/>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Probenzug</t>
+          <t>Probenzugsetikett(en) auf Probe(n) mit eingeklebtem(n) Etikett(en) identisch / Stage Etikett und Probenzugsetikett(en) in LIMS received, sowie Lagerort (03er Proben Lagerort = „in Bearbeitung“) angegeben</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>2026-06-10T08:14:00</t>
-        </is>
-      </c>
-      <c r="G306" t="inlineStr">
-        <is>
-          <t>Uhr</t>
+          <t>26.10.2025 / ohr</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -11415,27 +11413,23 @@
       <c r="C307" t="inlineStr"/>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Probenzugsetikett(en) auf Probe(n) mit eingeklebtem(n) Etikett(en) identisch</t>
+          <t>Probenzugsetikett(en) auf Probe(n) mit eingeklebtem(n) Etikett(en) identisch / Stage Etikett und Probenzugsetikett(en) in LIMS received, sowie Lagerort (03er Proben Lagerort = „in Bearbeitung“) angegeben</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>10.06.2025 / ohe</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>auto_accepted</t>
         </is>
       </c>
       <c r="I307" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J307" t="inlineStr">
-        <is>
-          <t>warning:EXTRACT_LOW_CONF</t>
-        </is>
-      </c>
+        <v>0.983</v>
+      </c>
+      <c r="J307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -11444,17 +11438,17 @@
         </is>
       </c>
       <c r="B308" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C308" t="inlineStr"/>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Stage Etikett und Probenzugsetikett(en) in LIMS received, sowie Lagerort (03er Proben Lagerort = „in Bearbeitung“) angegeben</t>
+          <t>Feld findet keine Anwendung</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>Nein</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
@@ -11478,28 +11472,32 @@
         </is>
       </c>
       <c r="B309" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C309" t="inlineStr"/>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Probenzugsetikett(en) auf Probe(n) mit eingeklebtem(n) Etikett(en) identisch</t>
+          <t>Ja / Nein, Feld findet keine Anwendung</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>26.10.2025 / ohr</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>auto_accepted</t>
+          <t>needs_review</t>
         </is>
       </c>
       <c r="I309" t="n">
-        <v>0.983</v>
-      </c>
-      <c r="J309" t="inlineStr"/>
+        <v>0.8</v>
+      </c>
+      <c r="J309" t="inlineStr">
+        <is>
+          <t>warning:EXTRACT_LOW_CONF</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -11508,17 +11506,17 @@
         </is>
       </c>
       <c r="B310" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C310" t="inlineStr"/>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Stage Etikett und Probenzugsetikett(en) in LIMS received, sowie Lagerort (03er Proben Lagerort = „in Bearbeitung“) angegeben</t>
+          <t>Bemerkungen</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>10.06.2025 / ohe</t>
+          <t>Fehler 404</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
@@ -11527,7 +11525,7 @@
         </is>
       </c>
       <c r="I310" t="n">
-        <v>0.983</v>
+        <v>1</v>
       </c>
       <c r="J310" t="inlineStr"/>
     </row>
@@ -11538,32 +11536,28 @@
         </is>
       </c>
       <c r="B311" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C311" t="inlineStr"/>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Ja / Nein, Feld findet keine Anwendung</t>
+          <t>Datum/Kürzel</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Nein</t>
+          <t>10.06.2026 / ohe</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>auto_accepted</t>
         </is>
       </c>
       <c r="I311" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J311" t="inlineStr">
-        <is>
-          <t>warning:EXTRACT_LOW_CONF</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="J311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -11577,27 +11571,23 @@
       <c r="C312" t="inlineStr"/>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Feld findet keine Anwendung</t>
+          <t>Bemerkungen</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>n.a. 10.06.2026 ohe</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>auto_accepted</t>
         </is>
       </c>
       <c r="I312" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J312" t="inlineStr">
-        <is>
-          <t>warning:EXTRACT_LOW_CONF</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="J312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -11606,28 +11596,32 @@
         </is>
       </c>
       <c r="B313" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C313" t="inlineStr"/>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Bemerkungen</t>
+          <t>Abweichungen vorhanden</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Fehler 404</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>auto_accepted</t>
+          <t>needs_review</t>
         </is>
       </c>
       <c r="I313" t="n">
-        <v>1</v>
-      </c>
-      <c r="J313" t="inlineStr"/>
+        <v>0.8</v>
+      </c>
+      <c r="J313" t="inlineStr">
+        <is>
+          <t>warning:EXTRACT_LOW_CONF</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -11636,17 +11630,22 @@
         </is>
       </c>
       <c r="B314" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C314" t="inlineStr"/>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>signature_processed</t>
+        </is>
+      </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Datum/Kürzel</t>
+          <t>Bearbeitet</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>10.06.2026 / ohe</t>
+          <t>10.06.2026 / Oly</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
@@ -11655,7 +11654,7 @@
         </is>
       </c>
       <c r="I314" t="n">
-        <v>1</v>
+        <v>0.961</v>
       </c>
       <c r="J314" t="inlineStr"/>
     </row>
@@ -11671,12 +11670,12 @@
       <c r="C315" t="inlineStr"/>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Abweichungen vorhanden.</t>
+          <t>zu Seite</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>17</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
@@ -11703,19 +11702,14 @@
         <v>44</v>
       </c>
       <c r="C316" t="inlineStr"/>
-      <c r="D316" t="inlineStr">
-        <is>
-          <t>signature_processed</t>
-        </is>
-      </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Bearbeitet: (Datum/Kürzel)</t>
+          <t>Referenz EV</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>10.06.2026 / olr</t>
+          <t>EV-2026-001</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
@@ -11724,7 +11718,7 @@
         </is>
       </c>
       <c r="I316" t="n">
-        <v>0.961</v>
+        <v>0.978</v>
       </c>
       <c r="J316" t="inlineStr"/>
     </row>
@@ -11740,27 +11734,23 @@
       <c r="C317" t="inlineStr"/>
       <c r="E317" t="inlineStr">
         <is>
-          <t>zu Seite</t>
+          <t>EV mündet in DEVI</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>DEVI-2026-001</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>auto_accepted</t>
         </is>
       </c>
       <c r="I317" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J317" t="inlineStr">
-        <is>
-          <t>warning:EXTRACT_LOW_CONF</t>
-        </is>
-      </c>
+        <v>0.978</v>
+      </c>
+      <c r="J317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -11774,12 +11764,12 @@
       <c r="C318" t="inlineStr"/>
       <c r="E318" t="inlineStr">
         <is>
-          <t>Referenz EV</t>
+          <t>Datum/Kürzel</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>EV-20 26 - 001</t>
+          <t>10.06.2026 / Oly</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
@@ -11788,7 +11778,7 @@
         </is>
       </c>
       <c r="I318" t="n">
-        <v>0.978</v>
+        <v>0.961</v>
       </c>
       <c r="J318" t="inlineStr"/>
     </row>
@@ -11804,23 +11794,27 @@
       <c r="C319" t="inlineStr"/>
       <c r="E319" t="inlineStr">
         <is>
-          <t>EV mündet in DEVI</t>
+          <t>Weitere Abweichungen</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>DEVI-20 26 - 001</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>auto_accepted</t>
+          <t>needs_review</t>
         </is>
       </c>
       <c r="I319" t="n">
-        <v>0.978</v>
-      </c>
-      <c r="J319" t="inlineStr"/>
+        <v>0.8</v>
+      </c>
+      <c r="J319" t="inlineStr">
+        <is>
+          <t>warning:EXTRACT_LOW_CONF</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -11834,23 +11828,27 @@
       <c r="C320" t="inlineStr"/>
       <c r="E320" t="inlineStr">
         <is>
-          <t>Datum/Kürzel</t>
+          <t>zu Seite</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>10.06.2026 / olr</t>
+          <t>34</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>auto_accepted</t>
+          <t>needs_review</t>
         </is>
       </c>
       <c r="I320" t="n">
-        <v>0.961</v>
-      </c>
-      <c r="J320" t="inlineStr"/>
+        <v>0.8</v>
+      </c>
+      <c r="J320" t="inlineStr">
+        <is>
+          <t>warning:EXTRACT_LOW_CONF</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -11864,27 +11862,23 @@
       <c r="C321" t="inlineStr"/>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Weitere Abweichungen</t>
+          <t>Referenz EV</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>EV-2025-043</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>auto_accepted</t>
         </is>
       </c>
       <c r="I321" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J321" t="inlineStr">
-        <is>
-          <t>warning:EXTRACT_LOW_CONF</t>
-        </is>
-      </c>
+        <v>0.978</v>
+      </c>
+      <c r="J321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -11898,27 +11892,23 @@
       <c r="C322" t="inlineStr"/>
       <c r="E322" t="inlineStr">
         <is>
-          <t>zu Seite</t>
+          <t>EV mündet in DEVI</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>DEVI-2025-014</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>auto_accepted</t>
         </is>
       </c>
       <c r="I322" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J322" t="inlineStr">
-        <is>
-          <t>warning:EXTRACT_LOW_CONF</t>
-        </is>
-      </c>
+        <v>0.978</v>
+      </c>
+      <c r="J322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -11932,12 +11922,12 @@
       <c r="C323" t="inlineStr"/>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Referenz EV</t>
+          <t>Datum/Kürzel</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>EV-20 25 - 043</t>
+          <t>10.06.2026 / ohp</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
@@ -11946,7 +11936,7 @@
         </is>
       </c>
       <c r="I323" t="n">
-        <v>0.978</v>
+        <v>0.961</v>
       </c>
       <c r="J323" t="inlineStr"/>
     </row>
@@ -11962,23 +11952,27 @@
       <c r="C324" t="inlineStr"/>
       <c r="E324" t="inlineStr">
         <is>
-          <t>EV mündet in DEVI</t>
+          <t>Weitere Abweichungen</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>DEVI-20 25 - 014</t>
+          <t>Nein, restliches Kapitel findet keine Anwendung</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>auto_accepted</t>
+          <t>needs_review</t>
         </is>
       </c>
       <c r="I324" t="n">
-        <v>0.978</v>
-      </c>
-      <c r="J324" t="inlineStr"/>
+        <v>0.8</v>
+      </c>
+      <c r="J324" t="inlineStr">
+        <is>
+          <t>warning:EXTRACT_LOW_CONF</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -11992,23 +11986,27 @@
       <c r="C325" t="inlineStr"/>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Datum/Kürzel</t>
+          <t>Referenz EV</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>10.06.2026 / olr</t>
+          <t>EV-20-</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>auto_accepted</t>
+          <t>needs_review</t>
         </is>
       </c>
       <c r="I325" t="n">
-        <v>0.961</v>
-      </c>
-      <c r="J325" t="inlineStr"/>
+        <v>0.8</v>
+      </c>
+      <c r="J325" t="inlineStr">
+        <is>
+          <t>warning:EXTRACT_LOW_CONF</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -12022,12 +12020,12 @@
       <c r="C326" t="inlineStr"/>
       <c r="E326" t="inlineStr">
         <is>
-          <t>Weitere Abweichungen</t>
+          <t>EV mündet in DEVI</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>Nein, restliches Kapitel findet keine Anwendung</t>
+          <t>DEVI-20-</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
@@ -12051,28 +12049,168 @@
         </is>
       </c>
       <c r="B327" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C327" t="inlineStr"/>
       <c r="E327" t="inlineStr">
         <is>
+          <t>Referenz EV</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>EV-20-</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>needs_review</t>
+        </is>
+      </c>
+      <c r="I327" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J327" t="inlineStr">
+        <is>
+          <t>warning:EXTRACT_LOW_CONF</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>scanned_batch_documentation.pdf</t>
+        </is>
+      </c>
+      <c r="B328" t="n">
+        <v>44</v>
+      </c>
+      <c r="C328" t="inlineStr"/>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>EV mündet in DEVI</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>DEVI-20-</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>needs_review</t>
+        </is>
+      </c>
+      <c r="I328" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J328" t="inlineStr">
+        <is>
+          <t>warning:EXTRACT_LOW_CONF</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>scanned_batch_documentation.pdf</t>
+        </is>
+      </c>
+      <c r="B329" t="n">
+        <v>44</v>
+      </c>
+      <c r="C329" t="inlineStr"/>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>Referenz EV</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>EV-20-</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>needs_review</t>
+        </is>
+      </c>
+      <c r="I329" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J329" t="inlineStr">
+        <is>
+          <t>warning:EXTRACT_LOW_CONF</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>scanned_batch_documentation.pdf</t>
+        </is>
+      </c>
+      <c r="B330" t="n">
+        <v>44</v>
+      </c>
+      <c r="C330" t="inlineStr"/>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>EV mündet in DEVI</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>DEVI-20-</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>needs_review</t>
+        </is>
+      </c>
+      <c r="I330" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J330" t="inlineStr">
+        <is>
+          <t>warning:EXTRACT_LOW_CONF</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>scanned_batch_documentation.pdf</t>
+        </is>
+      </c>
+      <c r="B331" t="n">
+        <v>45</v>
+      </c>
+      <c r="C331" t="inlineStr"/>
+      <c r="E331" t="inlineStr">
+        <is>
           <t>Review durchgeführt: Reviewer (Datum/Unterschrift)</t>
         </is>
       </c>
-      <c r="F327" t="inlineStr">
-        <is>
-          <t>10.06.2026 / GhP</t>
-        </is>
-      </c>
-      <c r="H327" t="inlineStr">
-        <is>
-          <t>auto_accepted</t>
-        </is>
-      </c>
-      <c r="I327" t="n">
-        <v>0.973</v>
-      </c>
-      <c r="J327" t="inlineStr"/>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>10.06.2026 / 6hp</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>needs_review</t>
+        </is>
+      </c>
+      <c r="I331" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J331" t="inlineStr">
+        <is>
+          <t>warning:EXTRACT_LOW_CONF</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12188,12 +12326,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>10.06.2026 / ohe</t>
+          <t>10.06.2026 / ohp</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10.06.2026 / olr</t>
+          <t>10.06.2026 / Oly</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
